--- a/ratings.xlsx
+++ b/ratings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\7sher\Documents\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{106159E4-7C3E-4EB4-9544-A8A4633E5FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C98D8ED2-E495-466C-B0FF-72FC29E96C49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1665" yWindow="1005" windowWidth="22200" windowHeight="14310" xr2:uid="{975520F9-B6E9-48FA-9812-89BEC17E316B}"/>
   </bookViews>
@@ -843,11 +843,11 @@
         <v>5</v>
       </c>
       <c r="G5" s="2">
-        <v>18</v>
+        <v>18.649999999999999</v>
       </c>
       <c r="H5" s="3">
         <f>G5/E5-1</f>
-        <v>-0.17469050894085281</v>
+        <v>-0.1448876662081614</v>
       </c>
       <c r="I5" t="s">
         <v>47</v>
@@ -895,11 +895,11 @@
         <v>5</v>
       </c>
       <c r="G6">
-        <v>9.64</v>
+        <v>8.77</v>
       </c>
       <c r="H6" s="3">
         <f>(G6/E6-1)*-1</f>
-        <v>3.0181086519114553E-2</v>
+        <v>0.11770623742454733</v>
       </c>
       <c r="I6" t="s">
         <v>48</v>
@@ -947,11 +947,11 @@
         <v>3</v>
       </c>
       <c r="G7" s="2">
-        <v>67</v>
+        <v>70.78</v>
       </c>
       <c r="H7" s="3">
         <f>G7/E7-1</f>
-        <v>-3.2211469016322436E-2</v>
+        <v>2.2389137657085056E-2</v>
       </c>
       <c r="I7" t="s">
         <v>49</v>
@@ -1079,11 +1079,11 @@
         <v>3</v>
       </c>
       <c r="G10" s="2">
-        <v>82.08</v>
+        <v>83.27</v>
       </c>
       <c r="H10" s="3">
         <f>G10/E10-1</f>
-        <v>6.5974025974026018E-2</v>
+        <v>8.1428571428571406E-2</v>
       </c>
       <c r="K10" s="5"/>
       <c r="L10">
@@ -1288,7 +1288,9 @@
       <c r="E15" s="2">
         <v>111.19</v>
       </c>
-      <c r="G15" s="2"/>
+      <c r="G15" s="2">
+        <v>120.5</v>
+      </c>
       <c r="H15" s="3"/>
       <c r="I15" t="s">
         <v>62</v>
@@ -1321,11 +1323,11 @@
         <v>3</v>
       </c>
       <c r="G16" s="2">
-        <v>15.74</v>
+        <v>15.88</v>
       </c>
       <c r="H16" s="3">
         <f>(G16/E16-1)*-1</f>
-        <v>-0.10301331464611074</v>
+        <v>-0.1128241065171689</v>
       </c>
       <c r="I16" t="s">
         <v>53</v>
@@ -1405,11 +1407,11 @@
         <v>18.600000000000001</v>
       </c>
       <c r="G18">
-        <v>20.64</v>
+        <v>21.16</v>
       </c>
       <c r="H18" s="3">
         <f>G18/E18-1</f>
-        <v>0.10967741935483866</v>
+        <v>0.13763440860215037</v>
       </c>
       <c r="I18" t="s">
         <v>55</v>
@@ -1495,11 +1497,11 @@
         <v>5</v>
       </c>
       <c r="G20" s="2">
-        <v>52.8</v>
+        <v>59.26</v>
       </c>
       <c r="H20" s="3">
         <f>G20/E20-1</f>
-        <v>0</v>
+        <v>0.12234848484848482</v>
       </c>
       <c r="I20" t="s">
         <v>56</v>
@@ -1544,7 +1546,7 @@
       </c>
       <c r="H23" s="3">
         <f>AVERAGE(H3:H20)</f>
-        <v>8.3853805150139737E-2</v>
+        <v>0.11117695748270767</v>
       </c>
       <c r="K23" s="5">
         <f>AVERAGE(K3:K20)</f>
@@ -1586,7 +1588,7 @@
       </c>
       <c r="H25" s="3">
         <f>AVERAGE(H14:H17,H8,H6,H3)</f>
-        <v>0.12881544910828843</v>
+        <v>0.14435832091516337</v>
       </c>
       <c r="J25" s="3">
         <f>SUM(J14:J17,J8,J6,J3)/COUNT(J14:J17,J8,J6,J3)</f>
@@ -1617,7 +1619,7 @@
       </c>
       <c r="H26" s="3">
         <f>AVERAGE(H13,H10,H7,H5)</f>
-        <v>-2.4362422778396009E-2</v>
+        <v>6.0207593676506188E-4</v>
       </c>
       <c r="J26" t="e">
         <f>SUM(J13,J10,J7,J5)/COUNT(J13,J10,J7,J5)</f>

--- a/ratings.xlsx
+++ b/ratings.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\7sher\Documents\models\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\7sher\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C98D8ED2-E495-466C-B0FF-72FC29E96C49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85BDAC88-B7D0-4E7E-BDFF-E218E443D147}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1665" yWindow="1005" windowWidth="22200" windowHeight="14310" xr2:uid="{975520F9-B6E9-48FA-9812-89BEC17E316B}"/>
+    <workbookView xWindow="1530" yWindow="1560" windowWidth="19470" windowHeight="12765" xr2:uid="{975520F9-B6E9-48FA-9812-89BEC17E316B}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="71">
   <si>
     <t>Date</t>
   </si>
@@ -230,9 +230,6 @@
     <t>QURE</t>
   </si>
   <si>
-    <t>update: 9/26</t>
-  </si>
-  <si>
     <t>CRNX</t>
   </si>
   <si>
@@ -243,6 +240,33 @@
   </si>
   <si>
     <t>Lots of market exposure to movement but long term this is likely to drop and I would add here to the short at this very high price as long as your position isn't too large</t>
+  </si>
+  <si>
+    <t>update: 4/23/2026</t>
+  </si>
+  <si>
+    <t>Current Date</t>
+  </si>
+  <si>
+    <t>Current FDA regulations not good for their business model and large DMD competition. Weak outlook.</t>
+  </si>
+  <si>
+    <t>Was wrong. Weak business model. Not a good moat. Bad bet. Better options.</t>
+  </si>
+  <si>
+    <t>Really good data for drug, likely approval. Currently holding. Really good market potential. Performance dependent on marketing.</t>
+  </si>
+  <si>
+    <t>Sell unless hedging, good hedge still.</t>
+  </si>
+  <si>
+    <t>Alright Long. Not the best currently.</t>
+  </si>
+  <si>
+    <t>HOLD</t>
+  </si>
+  <si>
+    <t>FDA regulatory pathway delayed. Still good data. Good potential.</t>
   </si>
 </sst>
 </file>
@@ -663,7 +687,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{054A6B13-8CAC-436C-8123-F4D415EF8DC4}">
-  <dimension ref="A1:V35"/>
+  <dimension ref="A1:V42"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
@@ -681,7 +705,7 @@
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A1" s="10" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B1" s="1"/>
       <c r="V1" t="s">
@@ -761,7 +785,7 @@
         <v>3</v>
       </c>
       <c r="G3">
-        <v>2.4900000000000002</v>
+        <v>1.67</v>
       </c>
       <c r="H3" s="3">
         <f>(E4/E3-1)*-1</f>
@@ -797,7 +821,7 @@
         <v>4.2700000000000002E-2</v>
       </c>
       <c r="V3" s="5">
-        <f>(F3*K3)/MIN(F3:F13)</f>
+        <f>(F3*K3)/MIN(F3:F15)</f>
         <v>0.39845362807704293</v>
       </c>
     </row>
@@ -843,23 +867,29 @@
         <v>5</v>
       </c>
       <c r="G5" s="2">
-        <v>18.649999999999999</v>
+        <v>20.420000000000002</v>
       </c>
       <c r="H5" s="3">
         <f>G5/E5-1</f>
-        <v>-0.1448876662081614</v>
+        <v>-6.3732232920678422E-2</v>
       </c>
       <c r="I5" t="s">
         <v>47</v>
       </c>
-      <c r="J5" t="s">
-        <v>45</v>
-      </c>
-      <c r="K5" s="5"/>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <f>H5-(R5+L5*((Q6/Q5)-1)-R5)</f>
+        <v>-0.11031858454511499</v>
+      </c>
       <c r="L5">
         <v>0.46</v>
       </c>
-      <c r="M5" s="3"/>
+      <c r="M5" s="3">
+        <f>H5/(DATEDIF(C5,$C$42,"d")/365)</f>
+        <v>-9.3799455709869459E-2</v>
+      </c>
       <c r="N5" t="s">
         <v>28</v>
       </c>
@@ -874,98 +904,80 @@
         <v>4.2700000000000002E-2</v>
       </c>
       <c r="V5" s="5">
-        <f>(F5*K5)/MIN(F5:F13)</f>
-        <v>0</v>
+        <f>(F5*K5)/MIN(F5:F15)</f>
+        <v>-0.18386430757519165</v>
       </c>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B6" t="s">
-        <v>2</v>
-      </c>
       <c r="C6" s="1">
-        <v>45887</v>
+        <v>46135</v>
       </c>
       <c r="D6" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="E6">
-        <v>9.94</v>
-      </c>
-      <c r="F6">
-        <v>5</v>
-      </c>
-      <c r="G6">
-        <v>8.77</v>
-      </c>
-      <c r="H6" s="3">
-        <f>(G6/E6-1)*-1</f>
-        <v>0.11770623742454733</v>
-      </c>
+        <v>20.420000000000002</v>
+      </c>
+      <c r="G6" s="2"/>
+      <c r="H6" s="3"/>
       <c r="I6" t="s">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="J6" t="s">
         <v>45</v>
       </c>
       <c r="K6" s="5"/>
-      <c r="L6" s="2">
-        <v>0.8</v>
-      </c>
       <c r="M6" s="3"/>
-      <c r="N6" t="s">
-        <v>28</v>
-      </c>
-      <c r="O6" s="8" t="s">
-        <v>37</v>
-      </c>
+      <c r="O6" s="8"/>
       <c r="P6" s="9"/>
       <c r="Q6" s="2">
-        <v>643.29999999999995</v>
-      </c>
-      <c r="R6" s="5">
-        <v>4.2700000000000002E-2</v>
-      </c>
-      <c r="V6" s="5">
-        <f>(F6*K6)/MIN(F6:F17)</f>
-        <v>0</v>
-      </c>
+        <v>708.45</v>
+      </c>
+      <c r="R6" s="5"/>
+      <c r="V6" s="5"/>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B7" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C7" s="1">
         <v>45887</v>
       </c>
       <c r="D7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E7">
-        <v>69.23</v>
+        <v>9.94</v>
       </c>
       <c r="F7">
-        <v>3</v>
-      </c>
-      <c r="G7" s="2">
-        <v>70.78</v>
+        <v>5</v>
+      </c>
+      <c r="G7">
+        <v>3.31</v>
       </c>
       <c r="H7" s="3">
-        <f>G7/E7-1</f>
-        <v>2.2389137657085056E-2</v>
+        <f>(G7/E7-1)*-1</f>
+        <v>0.66700201207243459</v>
       </c>
       <c r="I7" t="s">
-        <v>49</v>
-      </c>
-      <c r="J7" t="s">
-        <v>45</v>
-      </c>
-      <c r="K7" s="5"/>
-      <c r="L7">
-        <v>1.44</v>
-      </c>
-      <c r="M7" s="3"/>
+        <v>48</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+      <c r="K7" s="5">
+        <f>H7-(R7+L7*((Q8/Q7)-1)-R7)</f>
+        <v>0.58598227011689275</v>
+      </c>
+      <c r="L7" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="M7" s="3">
+        <f>H7/(DATEDIF(C7,$C$42,"d")/365)</f>
+        <v>0.98167634841305895</v>
+      </c>
       <c r="N7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O7" s="8" t="s">
         <v>37</v>
@@ -978,164 +990,152 @@
         <v>4.2700000000000002E-2</v>
       </c>
       <c r="V7" s="5">
-        <f>(F7*K7)/MIN(F7:F29)</f>
-        <v>0</v>
+        <f>(F7*K7)/MIN(F7:F21)</f>
+        <v>0.97663711686148791</v>
       </c>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B8" t="s">
-        <v>5</v>
-      </c>
       <c r="C8" s="1">
-        <v>45894</v>
+        <v>46135</v>
       </c>
       <c r="D8" t="s">
-        <v>18</v>
-      </c>
-      <c r="E8" s="2">
-        <v>5.3</v>
-      </c>
-      <c r="F8">
-        <v>5</v>
-      </c>
-      <c r="G8" s="2">
-        <v>0.84</v>
-      </c>
-      <c r="H8" s="3">
-        <f>(G8/E8-1)*-1</f>
-        <v>0.84150943396226419</v>
-      </c>
-      <c r="I8" t="s">
-        <v>51</v>
-      </c>
-      <c r="J8">
-        <v>1</v>
-      </c>
-      <c r="K8" s="5">
-        <f>H8-(R8+L8*((Q9/Q8)-1)-R8)</f>
-        <v>0.81702268749939444</v>
-      </c>
-      <c r="L8">
-        <v>0.95</v>
-      </c>
-      <c r="M8" s="3">
-        <f>H8/(DATEDIF(C8,C9,"d")/365)</f>
-        <v>9.5984669811320753</v>
-      </c>
-      <c r="N8" t="s">
-        <v>28</v>
-      </c>
-      <c r="O8" s="8" t="s">
-        <v>37</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="H8" s="3"/>
+      <c r="K8" s="5"/>
+      <c r="L8" s="2"/>
+      <c r="M8" s="3"/>
+      <c r="O8" s="8"/>
       <c r="P8" s="9"/>
       <c r="Q8" s="2">
-        <v>642.47</v>
-      </c>
-      <c r="R8" s="5">
-        <v>4.2700000000000002E-2</v>
-      </c>
-      <c r="V8" s="5">
-        <f>(F8*K8)/MIN(F8:F23)</f>
-        <v>1.3617044791656572</v>
-      </c>
+        <v>708.45</v>
+      </c>
+      <c r="R8" s="5"/>
+      <c r="V8" s="5"/>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="B9" t="s">
+        <v>3</v>
+      </c>
       <c r="C9" s="1">
-        <v>45926</v>
+        <v>45887</v>
       </c>
       <c r="D9" t="s">
-        <v>31</v>
-      </c>
-      <c r="E9" s="2">
-        <v>0.84</v>
-      </c>
-      <c r="G9" s="2"/>
-      <c r="H9" s="3"/>
-      <c r="K9" s="5"/>
-      <c r="M9" s="3"/>
-      <c r="O9" s="8"/>
+        <v>17</v>
+      </c>
+      <c r="E9">
+        <v>69.23</v>
+      </c>
+      <c r="F9">
+        <v>3</v>
+      </c>
+      <c r="G9" s="2">
+        <v>49.75</v>
+      </c>
+      <c r="H9" s="3">
+        <f>G9/E9-1</f>
+        <v>-0.28138090423226925</v>
+      </c>
+      <c r="I9" t="s">
+        <v>49</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9" s="5">
+        <f>H9-(R9+L9*((Q10/Q9)-1)-R9)</f>
+        <v>-0.42721643975224455</v>
+      </c>
+      <c r="L9">
+        <v>1.44</v>
+      </c>
+      <c r="M9" s="3">
+        <f>H9/(DATEDIF(C9,$C$42,"d")/365)</f>
+        <v>-0.41412915340636403</v>
+      </c>
+      <c r="N9" t="s">
+        <v>29</v>
+      </c>
+      <c r="O9" s="8" t="s">
+        <v>37</v>
+      </c>
       <c r="P9" s="9"/>
       <c r="Q9" s="2">
-        <v>659.03</v>
-      </c>
-      <c r="R9" s="5"/>
-      <c r="V9" s="5"/>
+        <v>643.29999999999995</v>
+      </c>
+      <c r="R9" s="5">
+        <v>4.2700000000000002E-2</v>
+      </c>
+      <c r="V9" s="5">
+        <f>(F9*K9)/MIN(F9:F36)</f>
+        <v>-0.4272164397522446</v>
+      </c>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B10" t="s">
-        <v>6</v>
-      </c>
       <c r="C10" s="1">
-        <v>45894</v>
+        <v>46135</v>
       </c>
       <c r="D10" t="s">
-        <v>17</v>
-      </c>
-      <c r="E10" s="2">
-        <v>77</v>
-      </c>
-      <c r="F10">
-        <v>3</v>
-      </c>
-      <c r="G10" s="2">
-        <v>83.27</v>
-      </c>
-      <c r="H10" s="3">
-        <f>G10/E10-1</f>
-        <v>8.1428571428571406E-2</v>
+        <v>31</v>
+      </c>
+      <c r="G10" s="2"/>
+      <c r="H10" s="3"/>
+      <c r="I10" t="s">
+        <v>65</v>
+      </c>
+      <c r="J10" t="s">
+        <v>45</v>
       </c>
       <c r="K10" s="5"/>
-      <c r="L10">
-        <v>1.58</v>
-      </c>
       <c r="M10" s="3"/>
-      <c r="N10" t="s">
-        <v>28</v>
-      </c>
-      <c r="O10" s="8" t="s">
-        <v>37</v>
-      </c>
+      <c r="O10" s="8"/>
       <c r="P10" s="9"/>
       <c r="Q10" s="2">
-        <v>642.47</v>
-      </c>
-      <c r="R10" s="5">
-        <v>4.2700000000000002E-2</v>
-      </c>
-      <c r="V10" s="5">
-        <f>(F10*K10)/MIN(F10:F24)</f>
-        <v>0</v>
-      </c>
+        <v>708.45</v>
+      </c>
+      <c r="R10" s="5"/>
+      <c r="V10" s="5"/>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B11" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C11" s="1">
         <v>45894</v>
       </c>
       <c r="D11" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E11" s="2">
-        <v>26</v>
+        <v>5.3</v>
+      </c>
+      <c r="F11">
+        <v>5</v>
       </c>
       <c r="G11" s="2">
-        <v>18.600000000000001</v>
-      </c>
-      <c r="H11" s="3"/>
+        <v>0.84</v>
+      </c>
+      <c r="H11" s="3">
+        <f>(E12/E11-1)*-1</f>
+        <v>0.84150943396226419</v>
+      </c>
       <c r="I11" t="s">
-        <v>54</v>
-      </c>
-      <c r="J11" t="s">
-        <v>45</v>
-      </c>
-      <c r="K11" s="5"/>
+        <v>51</v>
+      </c>
+      <c r="J11">
+        <v>1</v>
+      </c>
+      <c r="K11" s="5">
+        <f>H11-(R11+L11*((Q12/Q11)-1)-R11)</f>
+        <v>0.81702268749939444</v>
+      </c>
       <c r="L11">
-        <v>0.86</v>
-      </c>
-      <c r="M11" s="3"/>
+        <v>0.95</v>
+      </c>
+      <c r="M11" s="3">
+        <f>H11/(DATEDIF(C11,C12,"d")/365)</f>
+        <v>9.5984669811320753</v>
+      </c>
       <c r="N11" t="s">
         <v>28</v>
       </c>
@@ -1150,21 +1150,20 @@
         <v>4.2700000000000002E-2</v>
       </c>
       <c r="V11" s="5">
-        <f>(F11*K11)/MIN(F11:F28)</f>
-        <v>0</v>
+        <f>(F11*K11)/MIN(F11:F30)</f>
+        <v>1.3617044791656572</v>
       </c>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C12" s="1">
-        <v>45911</v>
+        <v>45926</v>
       </c>
       <c r="D12" t="s">
         <v>31</v>
       </c>
       <c r="E12" s="2">
-        <v>18.600000000000001</v>
-      </c>
-      <c r="F12" s="3"/>
+        <v>0.84</v>
+      </c>
       <c r="G12" s="2"/>
       <c r="H12" s="3"/>
       <c r="K12" s="5"/>
@@ -1172,14 +1171,14 @@
       <c r="O12" s="8"/>
       <c r="P12" s="9"/>
       <c r="Q12" s="2">
-        <v>657.63</v>
+        <v>659.03</v>
       </c>
       <c r="R12" s="5"/>
       <c r="V12" s="5"/>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B13" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C13" s="1">
         <v>45894</v>
@@ -1188,31 +1187,34 @@
         <v>17</v>
       </c>
       <c r="E13" s="2">
-        <v>46</v>
+        <v>77</v>
       </c>
       <c r="F13">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G13" s="2">
-        <v>48</v>
+        <v>113</v>
       </c>
       <c r="H13" s="3">
         <f>G13/E13-1</f>
-        <v>4.3478260869565188E-2</v>
+        <v>0.46753246753246747</v>
       </c>
       <c r="I13" t="s">
-        <v>46</v>
-      </c>
-      <c r="J13" t="s">
-        <v>45</v>
+        <v>66</v>
+      </c>
+      <c r="J13">
+        <v>1</v>
       </c>
       <c r="K13" s="5"/>
       <c r="L13">
-        <v>0.91</v>
-      </c>
-      <c r="M13" s="3"/>
+        <v>1.58</v>
+      </c>
+      <c r="M13" s="3">
+        <f>H13/(DATEDIF(C13,$C$42,"d")/365)</f>
+        <v>0.70808859190601925</v>
+      </c>
       <c r="N13" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="O13" s="8" t="s">
         <v>37</v>
@@ -1231,84 +1233,108 @@
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B14" t="s">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="C14" s="1">
-        <v>45897</v>
+        <v>45894</v>
       </c>
       <c r="D14" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="E14" s="2">
-        <v>73</v>
-      </c>
-      <c r="F14">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="G14" s="2">
-        <v>111.19</v>
-      </c>
-      <c r="H14" s="3">
-        <f>(G14/E14-1)*-1</f>
-        <v>-0.52315068493150685</v>
-      </c>
+        <v>22.27</v>
+      </c>
+      <c r="H14" s="3"/>
       <c r="I14" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="J14" t="s">
         <v>45</v>
       </c>
       <c r="K14" s="5"/>
       <c r="L14">
-        <v>0.62</v>
+        <v>0.86</v>
       </c>
       <c r="M14" s="3"/>
       <c r="N14" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="O14" s="8" t="s">
         <v>37</v>
       </c>
       <c r="P14" s="9"/>
       <c r="Q14" s="2">
-        <v>647</v>
+        <v>642.47</v>
       </c>
       <c r="R14" s="5">
-        <v>4.2299999999999997E-2</v>
-      </c>
-      <c r="V14" s="5"/>
+        <v>4.2700000000000002E-2</v>
+      </c>
+      <c r="V14" s="5">
+        <f>(F14*K14)/MIN(F14:F35)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="B15" t="s">
+        <v>7</v>
+      </c>
       <c r="C15" s="1">
-        <v>45926</v>
+        <v>45894</v>
       </c>
       <c r="D15" t="s">
-        <v>61</v>
+        <v>17</v>
       </c>
       <c r="E15" s="2">
-        <v>111.19</v>
+        <v>46</v>
+      </c>
+      <c r="F15">
+        <v>5</v>
       </c>
       <c r="G15" s="2">
-        <v>120.5</v>
-      </c>
-      <c r="H15" s="3"/>
+        <v>57.83</v>
+      </c>
+      <c r="H15" s="3">
+        <f>G15/E15-1</f>
+        <v>0.25717391304347825</v>
+      </c>
       <c r="I15" t="s">
-        <v>62</v>
-      </c>
-      <c r="J15" t="s">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="J15">
+        <v>1</v>
       </c>
       <c r="K15" s="5"/>
-      <c r="M15" s="3"/>
-      <c r="O15" s="8"/>
+      <c r="L15">
+        <v>0.91</v>
+      </c>
+      <c r="M15" s="3">
+        <f>H15/(DATEDIF(C15,$C$42,"d")/365)</f>
+        <v>0.38949576041854594</v>
+      </c>
+      <c r="N15" t="s">
+        <v>30</v>
+      </c>
+      <c r="O15" s="8" t="s">
+        <v>37</v>
+      </c>
       <c r="P15" s="9"/>
-      <c r="Q15" s="2"/>
-      <c r="R15" s="5"/>
-      <c r="V15" s="5"/>
+      <c r="Q15" s="2">
+        <v>642.47</v>
+      </c>
+      <c r="R15" s="5">
+        <v>4.2700000000000002E-2</v>
+      </c>
+      <c r="V15" s="5">
+        <f>(F15*K15)/MIN(F15:F38)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B16" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C16" s="1">
         <v>45897</v>
@@ -1317,31 +1343,37 @@
         <v>18</v>
       </c>
       <c r="E16" s="2">
-        <v>14.27</v>
+        <v>73</v>
       </c>
       <c r="F16">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G16" s="2">
-        <v>15.88</v>
+        <v>76.459999999999994</v>
       </c>
       <c r="H16" s="3">
-        <f>(G16/E16-1)*-1</f>
-        <v>-0.1128241065171689</v>
+        <f>(E18/(AVERAGE(E16:E17))-1)*-1</f>
+        <v>0.38433139692708618</v>
       </c>
       <c r="I16" t="s">
-        <v>53</v>
-      </c>
-      <c r="J16" t="s">
-        <v>45</v>
-      </c>
-      <c r="K16" s="5"/>
+        <v>52</v>
+      </c>
+      <c r="J16">
+        <v>1</v>
+      </c>
+      <c r="K16" s="5">
+        <f>H16-(R16+L16*((Q17/Q16)-1)-R16)</f>
+        <v>0.32544577096108923</v>
+      </c>
       <c r="L16">
-        <v>2.52</v>
-      </c>
-      <c r="M16" s="3"/>
+        <v>0.62</v>
+      </c>
+      <c r="M16" s="3">
+        <f>H16/(DATEDIF(C16,C17,"d")/365)</f>
+        <v>4.8372744785650497</v>
+      </c>
       <c r="N16" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="O16" s="8" t="s">
         <v>37</v>
@@ -1356,421 +1388,666 @@
       <c r="V16" s="5"/>
     </row>
     <row r="17" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="B17" t="s">
-        <v>41</v>
-      </c>
       <c r="C17" s="1">
-        <v>45897</v>
+        <v>45926</v>
       </c>
       <c r="D17" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="E17" s="2">
-        <v>338.84</v>
-      </c>
-      <c r="F17">
-        <v>4</v>
-      </c>
-      <c r="G17" s="2">
-        <v>304.93</v>
-      </c>
+        <v>111.19</v>
+      </c>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="3"/>
       <c r="I17" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="J17" t="s">
         <v>45</v>
       </c>
-      <c r="L17">
-        <v>3.78</v>
-      </c>
-      <c r="N17" t="s">
-        <v>42</v>
-      </c>
+      <c r="K17" s="5"/>
+      <c r="M17" s="3">
+        <f>H16/(DATEDIF(C16,C18,"d")/365)</f>
+        <v>0.69446019741775478</v>
+      </c>
+      <c r="O17" s="8"/>
+      <c r="P17" s="9"/>
       <c r="Q17" s="2">
-        <v>647</v>
-      </c>
-      <c r="R17" s="5">
-        <v>4.2299999999999997E-2</v>
-      </c>
+        <v>708.45</v>
+      </c>
+      <c r="R17" s="5"/>
+      <c r="V17" s="5"/>
     </row>
     <row r="18" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="B18" t="s">
-        <v>8</v>
-      </c>
       <c r="C18" s="1">
-        <v>45911</v>
+        <v>46099</v>
       </c>
       <c r="D18" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="E18" s="2">
-        <v>18.600000000000001</v>
-      </c>
-      <c r="G18">
-        <v>21.16</v>
-      </c>
-      <c r="H18" s="3">
-        <f>G18/E18-1</f>
-        <v>0.13763440860215037</v>
-      </c>
+        <v>56.7</v>
+      </c>
+      <c r="G18" s="2"/>
+      <c r="H18" s="3"/>
       <c r="I18" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="J18" t="s">
         <v>45</v>
       </c>
-      <c r="L18">
-        <v>0.87</v>
-      </c>
-      <c r="N18" t="s">
-        <v>28</v>
-      </c>
-      <c r="O18" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q18" s="2">
-        <v>657.63</v>
-      </c>
-      <c r="R18" s="5">
-        <v>4.0340000000000001E-2</v>
-      </c>
+      <c r="K18" s="5"/>
+      <c r="M18" s="3"/>
+      <c r="O18" s="8"/>
+      <c r="P18" s="9"/>
+      <c r="Q18" s="2"/>
+      <c r="R18" s="5"/>
+      <c r="V18" s="5"/>
     </row>
     <row r="19" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B19" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="C19" s="1">
-        <v>45922</v>
+        <v>45897</v>
       </c>
       <c r="D19" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E19" s="2">
-        <v>33.72</v>
+        <v>14.27</v>
       </c>
       <c r="F19">
         <v>3</v>
       </c>
       <c r="G19" s="2">
-        <v>45.52</v>
+        <v>8.49</v>
       </c>
       <c r="H19" s="3">
-        <f>G19/E19-1</f>
-        <v>0.34994068801897993</v>
+        <f>(E20/E19-1)*-1</f>
+        <v>0.40504555010511556</v>
       </c>
       <c r="I19" t="s">
-        <v>60</v>
-      </c>
-      <c r="J19" t="s">
-        <v>45</v>
-      </c>
-      <c r="L19" s="2">
-        <v>0.3</v>
+        <v>53</v>
+      </c>
+      <c r="J19">
+        <v>1</v>
+      </c>
+      <c r="K19" s="5">
+        <f>H19-(R19+L19*((Q20/Q19)-1)-R19)</f>
+        <v>0.16570397359816025</v>
+      </c>
+      <c r="L19">
+        <v>2.52</v>
+      </c>
+      <c r="M19" s="3">
+        <f>H19/(DATEDIF(C19,$C$42,"d")/365)</f>
+        <v>0.62118330163179492</v>
       </c>
       <c r="N19" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="O19" s="8" t="s">
         <v>37</v>
       </c>
+      <c r="P19" s="9"/>
       <c r="Q19" s="2">
-        <v>662.2</v>
+        <v>647</v>
       </c>
       <c r="R19" s="5">
-        <v>4.1399999999999999E-2</v>
-      </c>
+        <v>4.2299999999999997E-2</v>
+      </c>
+      <c r="V19" s="5"/>
     </row>
     <row r="20" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="B20" t="s">
-        <v>57</v>
-      </c>
       <c r="C20" s="1">
-        <v>45926</v>
+        <v>46135</v>
       </c>
       <c r="D20" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="E20" s="2">
-        <v>52.8</v>
-      </c>
-      <c r="F20">
-        <v>5</v>
-      </c>
-      <c r="G20" s="2">
-        <v>59.26</v>
-      </c>
-      <c r="H20" s="3">
-        <f>G20/E20-1</f>
-        <v>0.12234848484848482</v>
-      </c>
+        <v>8.49</v>
+      </c>
+      <c r="G20" s="2"/>
+      <c r="H20" s="3"/>
       <c r="I20" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="J20" t="s">
         <v>45</v>
       </c>
-      <c r="L20">
-        <v>1.45</v>
-      </c>
-      <c r="N20" t="s">
+      <c r="K20" s="5"/>
+      <c r="M20" s="3"/>
+      <c r="O20" s="8"/>
+      <c r="P20" s="9"/>
+      <c r="Q20" s="2">
+        <v>708.45</v>
+      </c>
+      <c r="R20" s="5"/>
+      <c r="V20" s="5"/>
+    </row>
+    <row r="21" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="B21" t="s">
+        <v>41</v>
+      </c>
+      <c r="C21" s="1">
+        <v>45897</v>
+      </c>
+      <c r="D21" t="s">
+        <v>38</v>
+      </c>
+      <c r="E21" s="2">
+        <v>338.84</v>
+      </c>
+      <c r="F21">
+        <v>4</v>
+      </c>
+      <c r="G21" s="2">
+        <v>172.47</v>
+      </c>
+      <c r="I21" t="s">
+        <v>50</v>
+      </c>
+      <c r="J21" t="s">
+        <v>45</v>
+      </c>
+      <c r="L21">
+        <v>3.78</v>
+      </c>
+      <c r="M21" s="3">
+        <f>H21/(DATEDIF(C21,$C$42,"d")/365)</f>
+        <v>0</v>
+      </c>
+      <c r="N21" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q21" s="2">
+        <v>647</v>
+      </c>
+      <c r="R21" s="5">
+        <v>4.2299999999999997E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="B22" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="1">
+        <v>45911</v>
+      </c>
+      <c r="D22" t="s">
+        <v>17</v>
+      </c>
+      <c r="E22" s="2">
+        <v>18.600000000000001</v>
+      </c>
+      <c r="G22">
+        <v>22.27</v>
+      </c>
+      <c r="H22" s="3">
+        <f>E23/E22-1</f>
+        <v>0.19731182795698921</v>
+      </c>
+      <c r="I22" t="s">
+        <v>55</v>
+      </c>
+      <c r="J22">
+        <v>1</v>
+      </c>
+      <c r="K22" s="5">
+        <f>H22-(R22+L22*((Q23/Q22)-1)-R22)</f>
+        <v>0.13008040603280679</v>
+      </c>
+      <c r="L22">
+        <v>0.87</v>
+      </c>
+      <c r="M22" s="3">
+        <f>H22/(DATEDIF(C22,$C$42,"d")/365)</f>
+        <v>0.32151257680491541</v>
+      </c>
+      <c r="N22" t="s">
         <v>28</v>
       </c>
-      <c r="O20" s="8"/>
-      <c r="Q20" s="2">
-        <v>659.03</v>
-      </c>
-      <c r="R20" s="5">
-        <v>4.1799999999999997E-2</v>
-      </c>
-    </row>
-    <row r="21" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="I21" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="J21" s="3">
-        <f>SUM(J3:J17)/COUNT(J3:J17)</f>
+      <c r="O22" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q22" s="2">
+        <v>657.63</v>
+      </c>
+      <c r="R22" s="5">
+        <v>4.0340000000000001E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="C23" s="1">
+        <v>46135</v>
+      </c>
+      <c r="D23" t="s">
+        <v>31</v>
+      </c>
+      <c r="E23">
+        <v>22.27</v>
+      </c>
+      <c r="H23" s="3"/>
+      <c r="I23" t="s">
+        <v>68</v>
+      </c>
+      <c r="J23" t="s">
+        <v>45</v>
+      </c>
+      <c r="M23" s="3"/>
+      <c r="O23" s="8"/>
+      <c r="Q23" s="2">
+        <v>708.45</v>
+      </c>
+      <c r="R23" s="5"/>
+    </row>
+    <row r="24" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="B24" t="s">
+        <v>58</v>
+      </c>
+      <c r="C24" s="1">
+        <v>45922</v>
+      </c>
+      <c r="D24" t="s">
+        <v>17</v>
+      </c>
+      <c r="E24" s="2">
+        <v>33.72</v>
+      </c>
+      <c r="F24">
+        <v>3</v>
+      </c>
+      <c r="G24" s="2">
+        <v>38.51</v>
+      </c>
+      <c r="H24" s="3">
+        <f>G24/E24-1</f>
+        <v>0.14205219454329776</v>
+      </c>
+      <c r="I24" t="s">
+        <v>59</v>
+      </c>
+      <c r="J24">
         <v>1</v>
       </c>
-    </row>
-    <row r="22" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="I22" s="7"/>
-      <c r="J22" s="3"/>
-    </row>
-    <row r="23" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="B23" t="s">
-        <v>26</v>
-      </c>
-      <c r="F23" s="2">
-        <f>AVERAGE(F3:F17)</f>
-        <v>3.9</v>
-      </c>
-      <c r="H23" s="3">
-        <f>AVERAGE(H3:H20)</f>
-        <v>0.11117695748270767</v>
-      </c>
-      <c r="K23" s="5">
-        <f>AVERAGE(K3:K20)</f>
-        <v>0.60773815778821871</v>
-      </c>
-      <c r="L23" s="2">
-        <f>AVERAGE(L3:L20)</f>
-        <v>1.2914285714285714</v>
-      </c>
-      <c r="M23" s="3">
-        <f>AVERAGE(M3:M13)</f>
-        <v>16.921818031628838</v>
-      </c>
-      <c r="V23" s="5">
-        <f>AVERAGE(V3:V13)</f>
-        <v>0.22001976340533752</v>
-      </c>
-    </row>
-    <row r="24" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="H24" s="5"/>
-      <c r="K24" s="5"/>
-      <c r="V24" s="5"/>
+      <c r="K24" s="5">
+        <f>H24-(R24+L24*((Q25/Q24)-1)-R24)</f>
+        <v>0.12109931021832041</v>
+      </c>
+      <c r="L24" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="M24" s="3">
+        <f>H24/(DATEDIF(C24,$C$42,"d")/365)</f>
+        <v>0.24342277468687173</v>
+      </c>
+      <c r="N24" t="s">
+        <v>28</v>
+      </c>
+      <c r="O24" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q24" s="2">
+        <v>662.2</v>
+      </c>
+      <c r="R24" s="5">
+        <v>4.1399999999999999E-2</v>
+      </c>
     </row>
     <row r="25" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="B25" t="s">
-        <v>18</v>
-      </c>
-      <c r="D25">
-        <f>COUNTIF(D3:D17,"SHORT")</f>
-        <v>5</v>
-      </c>
-      <c r="E25" s="3">
-        <f>D25/$D$27</f>
-        <v>0.55555555555555558</v>
-      </c>
-      <c r="F25" s="2">
-        <f>AVERAGE(F14:F17,F8,F6,F3)</f>
-        <v>3.8333333333333335</v>
-      </c>
-      <c r="H25" s="3">
-        <f>AVERAGE(H14:H17,H8,H6,H3)</f>
-        <v>0.14435832091516337</v>
-      </c>
-      <c r="J25" s="3">
-        <f>SUM(J14:J17,J8,J6,J3)/COUNT(J14:J17,J8,J6,J3)</f>
-        <v>1</v>
-      </c>
-      <c r="K25" s="3"/>
-      <c r="L25" s="2">
-        <f>AVERAGE(L14:L17,L8,L6,L3)</f>
-        <v>1.7016666666666669</v>
-      </c>
-      <c r="V25" s="5"/>
+      <c r="C25" s="1">
+        <v>45926</v>
+      </c>
+      <c r="D25" t="s">
+        <v>31</v>
+      </c>
+      <c r="E25" s="2">
+        <v>45.91</v>
+      </c>
+      <c r="G25" s="2"/>
+      <c r="H25" s="3"/>
+      <c r="J25" t="s">
+        <v>45</v>
+      </c>
+      <c r="L25" s="2"/>
+      <c r="M25" s="3"/>
+      <c r="O25" s="8"/>
+      <c r="Q25" s="2">
+        <v>708.45</v>
+      </c>
+      <c r="R25" s="5"/>
     </row>
     <row r="26" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B26" t="s">
+        <v>57</v>
+      </c>
+      <c r="C26" s="1">
+        <v>45926</v>
+      </c>
+      <c r="D26" t="s">
         <v>17</v>
       </c>
-      <c r="D26">
-        <f>COUNTIF(D3:D17,"LONG")</f>
-        <v>4</v>
-      </c>
-      <c r="E26" s="3">
-        <f>D26/$D$27</f>
-        <v>0.44444444444444442</v>
-      </c>
-      <c r="F26" s="2">
-        <f>AVERAGE(F13,F10,F7,F5)</f>
-        <v>4</v>
+      <c r="E26" s="2">
+        <v>52.8</v>
+      </c>
+      <c r="F26">
+        <v>5</v>
+      </c>
+      <c r="G26" s="2">
+        <v>17.54</v>
       </c>
       <c r="H26" s="3">
-        <f>AVERAGE(H13,H10,H7,H5)</f>
-        <v>6.0207593676506188E-4</v>
-      </c>
-      <c r="J26" t="e">
-        <f>SUM(J13,J10,J7,J5)/COUNT(J13,J10,J7,J5)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K26" s="2"/>
-      <c r="L26" s="2">
-        <f>AVERAGE(L13,L10,L7,L5)</f>
-        <v>1.0975000000000001</v>
-      </c>
-      <c r="V26" s="5"/>
+        <f>G26/E26-1</f>
+        <v>-0.66780303030303023</v>
+      </c>
+      <c r="I26" t="s">
+        <v>56</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26" s="5">
+        <f>H26-(R26+L26*((Q27/Q26)-1)-R26)</f>
+        <v>-0.77653707882889433</v>
+      </c>
+      <c r="L26">
+        <v>1.45</v>
+      </c>
+      <c r="M26" s="3">
+        <f>H26/(DATEDIF(C26,$C$42,"d")/365)</f>
+        <v>-1.1662588806727563</v>
+      </c>
+      <c r="N26" t="s">
+        <v>28</v>
+      </c>
+      <c r="O26" s="8"/>
+      <c r="Q26" s="2">
+        <v>659.03</v>
+      </c>
+      <c r="R26" s="5">
+        <v>4.1799999999999997E-2</v>
+      </c>
     </row>
     <row r="27" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="D27">
-        <f>SUM(D25:D26)</f>
-        <v>9</v>
-      </c>
-      <c r="H27" s="5"/>
-      <c r="K27" s="5"/>
-      <c r="V27" s="5"/>
+      <c r="C27" s="1">
+        <v>46135</v>
+      </c>
+      <c r="D27" t="s">
+        <v>69</v>
+      </c>
+      <c r="E27" s="2">
+        <v>17.54</v>
+      </c>
+      <c r="G27" s="2"/>
+      <c r="H27" s="3"/>
+      <c r="I27" t="s">
+        <v>70</v>
+      </c>
+      <c r="J27" t="s">
+        <v>45</v>
+      </c>
+      <c r="M27" s="3"/>
+      <c r="O27" s="8"/>
+      <c r="Q27" s="2">
+        <v>708.45</v>
+      </c>
+      <c r="R27" s="5"/>
     </row>
     <row r="28" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="B28" t="s">
-        <v>4</v>
-      </c>
-      <c r="C28" s="1">
-        <v>45862</v>
-      </c>
-      <c r="E28" s="2">
-        <v>634.41999999999996</v>
-      </c>
-      <c r="G28" s="2">
-        <v>645.04999999999995</v>
-      </c>
-      <c r="H28" s="3">
-        <f>G28/E28-1</f>
-        <v>1.6755461681535966E-2</v>
-      </c>
-      <c r="I28" s="3"/>
-      <c r="K28" s="5">
-        <f>H28-($H$29+L28*($H$28-$H$29))</f>
-        <v>0</v>
-      </c>
-      <c r="L28">
-        <v>1</v>
+      <c r="I28" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="J28" s="3">
+        <f>SUM(J3:J27)/COUNT(J3:J27)</f>
+        <v>0.75</v>
       </c>
     </row>
     <row r="29" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="B29" t="s">
-        <v>20</v>
-      </c>
-      <c r="C29" s="1"/>
-      <c r="H29" s="5">
-        <v>4.2700000000000002E-2</v>
-      </c>
-      <c r="I29" s="3"/>
-      <c r="K29" s="5">
-        <f>H29-($H$29+L29*($H$28-$H$29))</f>
-        <v>0</v>
-      </c>
-      <c r="L29">
-        <v>0</v>
-      </c>
+      <c r="I29" s="7"/>
+      <c r="J29" s="3"/>
     </row>
     <row r="30" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="J30" t="s">
-        <v>22</v>
+      <c r="B30" t="s">
+        <v>26</v>
+      </c>
+      <c r="F30" s="2">
+        <f>AVERAGE(F3:F21)</f>
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="H30" s="3">
+        <f>AVERAGE(H3:H26)</f>
+        <v>0.22896611277706969</v>
+      </c>
+      <c r="K30" s="5">
+        <f>AVERAGE(K3:K26)</f>
+        <v>0.12297159433774532</v>
+      </c>
+      <c r="L30" s="2">
+        <f>AVERAGE(L26,L24,L22,-L19,-L16,L15,L13,-L11,L9,-L7,L5,-L3)</f>
+        <v>4.8333333333333339E-2</v>
+      </c>
+      <c r="M30" s="3">
+        <f>AVERAGE(M3:M26)</f>
+        <v>2.9261830430937641</v>
+      </c>
+      <c r="V30" s="5">
+        <f>AVERAGE(V3:V15)</f>
+        <v>0.26571430959709397</v>
       </c>
     </row>
     <row r="31" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="B31" t="s">
-        <v>28</v>
-      </c>
-      <c r="J31" s="3">
-        <f>SUM(J3,J5,J6,J8,J10,J11)/COUNT(J3,J5,J6,J8,J10,J11)</f>
-        <v>1</v>
-      </c>
-      <c r="K31" s="5">
-        <f>AVERAGE(K3,K5,K6,K8,K10,K11)</f>
-        <v>0.60773815778821871</v>
-      </c>
-      <c r="L31" s="2">
-        <f>AVERAGE(L3,L5,L6,L8,L10,L11)</f>
-        <v>1.0316666666666667</v>
-      </c>
-      <c r="M31" s="3">
-        <f>AVERAGE(M3,M5,M6,M8,M10,M11)</f>
-        <v>16.921818031628838</v>
-      </c>
+      <c r="H31" s="5"/>
+      <c r="K31" s="5"/>
+      <c r="V31" s="5"/>
     </row>
     <row r="32" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B32" t="s">
+        <v>18</v>
+      </c>
+      <c r="D32">
+        <f>COUNTIF(D3:D21,"SHORT")</f>
+        <v>5</v>
+      </c>
+      <c r="E32" s="3">
+        <f>D32/$D$34</f>
+        <v>0.55555555555555558</v>
+      </c>
+      <c r="F32" s="2">
+        <f>AVERAGE(F16:F21,F11,F7,F3)</f>
+        <v>4.166666666666667</v>
+      </c>
+      <c r="H32" s="3">
+        <f>AVERAGE(H16:H21,H11,H7,H3)</f>
+        <v>0.53928782354091642</v>
+      </c>
+      <c r="J32" s="3">
+        <f>SUM(J16:J21,J11,J7,J3)/COUNT(J16:J21,J11,J7,J3)</f>
+        <v>1</v>
+      </c>
+      <c r="K32" s="3"/>
+      <c r="L32" s="2"/>
+      <c r="V32" s="5"/>
+    </row>
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="B33" t="s">
+        <v>17</v>
+      </c>
+      <c r="D33">
+        <f>COUNTIF(D3:D21,"LONG")</f>
+        <v>4</v>
+      </c>
+      <c r="E33" s="3">
+        <f>D33/$D$34</f>
+        <v>0.44444444444444442</v>
+      </c>
+      <c r="F33" s="2">
+        <f>AVERAGE(F15,F13,F9,F5)</f>
+        <v>4</v>
+      </c>
+      <c r="H33" s="3">
+        <f>AVERAGE(H15,H13,H9,H5,H22,H24,H26)</f>
+        <v>7.3077479457506834E-3</v>
+      </c>
+      <c r="J33" s="3">
+        <f>SUM(J15,J13,J9,J5,J22,J24,J26)/COUNT(J15,J13,J9,J5,J22,J24,J26)</f>
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="K33" s="2"/>
+      <c r="L33" s="2"/>
+      <c r="V33" s="5"/>
+    </row>
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="D34">
+        <f>SUM(D32:D33)</f>
+        <v>9</v>
+      </c>
+      <c r="H34" s="5"/>
+      <c r="K34" s="5"/>
+      <c r="V34" s="5"/>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="B35" t="s">
+        <v>4</v>
+      </c>
+      <c r="C35" s="1">
+        <v>45862</v>
+      </c>
+      <c r="E35" s="2">
+        <v>634.41999999999996</v>
+      </c>
+      <c r="G35" s="2">
+        <v>708.45</v>
+      </c>
+      <c r="H35" s="3">
+        <f>G35/E35-1</f>
+        <v>0.11668925948110109</v>
+      </c>
+      <c r="I35" s="3"/>
+      <c r="K35" s="5">
+        <f>H35-($H$36+L35*($H$35-$H$36))</f>
+        <v>0</v>
+      </c>
+      <c r="L35">
+        <v>1</v>
+      </c>
+      <c r="M35" s="3">
+        <f>H35/(DATEDIF(C35,$C$42,"d")/365)</f>
+        <v>0.15601311249304725</v>
+      </c>
+    </row>
+    <row r="36" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="B36" t="s">
+        <v>20</v>
+      </c>
+      <c r="C36" s="1"/>
+      <c r="H36" s="5">
+        <v>4.2999999999999997E-2</v>
+      </c>
+      <c r="I36" s="3"/>
+      <c r="K36" s="5">
+        <f>H36-($H$36+L36*($H$35-$H$36))</f>
+        <v>0</v>
+      </c>
+      <c r="L36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="J37" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="B38" t="s">
+        <v>28</v>
+      </c>
+      <c r="J38" s="3">
+        <f>SUM(J3,J5,J7,J11,J13,J14)/COUNT(J3,J5,J7,J11,J13,J14)</f>
+        <v>0.8</v>
+      </c>
+      <c r="K38" s="5">
+        <f>AVERAGE(K3,K5,K7,K11,K13,K14)</f>
+        <v>0.42278500028705379</v>
+      </c>
+      <c r="L38" s="2">
+        <f>AVERAGE(L3,L5,L7,L11,L13,L14)</f>
+        <v>1.0316666666666667</v>
+      </c>
+      <c r="M38" s="3">
+        <f>AVERAGE(M3,M5,M7,M11,M13,M14)</f>
+        <v>7.0879203095733772</v>
+      </c>
+    </row>
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="B39" t="s">
         <v>29</v>
       </c>
-      <c r="J32" t="e">
-        <f>SUM(J7)/COUNT(J7)</f>
+      <c r="J39">
+        <f>SUM(J9)/COUNT(J9)</f>
+        <v>0</v>
+      </c>
+      <c r="K39" s="5">
+        <f>AVERAGE(K9)</f>
+        <v>-0.42721643975224455</v>
+      </c>
+      <c r="L39" s="2">
+        <f>AVERAGE(L9)</f>
+        <v>1.44</v>
+      </c>
+      <c r="M39" s="3">
+        <f>AVERAGE(M9)</f>
+        <v>-0.41412915340636403</v>
+      </c>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="B40" t="s">
+        <v>30</v>
+      </c>
+      <c r="I40" s="3"/>
+      <c r="J40">
+        <f>SUM(J15)/COUNT(J15)</f>
+        <v>1</v>
+      </c>
+      <c r="K40" s="5" t="e">
+        <f>AVERAGE(K15)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="K32" s="5" t="e">
-        <f>AVERAGE(K7)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L32" s="2">
-        <f>AVERAGE(L7)</f>
-        <v>1.44</v>
-      </c>
-      <c r="M32" s="3" t="e">
-        <f>AVERAGE(M7)</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B33" t="s">
-        <v>30</v>
-      </c>
-      <c r="I33" s="3"/>
-      <c r="J33" t="e">
-        <f>SUM(J13)/COUNT(J13)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K33" s="5" t="e">
-        <f>AVERAGE(K13)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L33" s="2">
-        <f>AVERAGE(L13)</f>
+      <c r="L40" s="2">
+        <f>AVERAGE(L15)</f>
         <v>0.91</v>
       </c>
-      <c r="M33" s="3" t="e">
-        <f>AVERAGE(M13)</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="K35" s="5"/>
+      <c r="M40" s="3">
+        <f>AVERAGE(M15)</f>
+        <v>0.38949576041854594</v>
+      </c>
+    </row>
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="B42" t="s">
+        <v>63</v>
+      </c>
+      <c r="C42" s="1">
+        <v>46135</v>
+      </c>
+      <c r="K42" s="5"/>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="O3" r:id="rId1" xr:uid="{D28EB580-B8E1-48AE-8C56-94A069342149}"/>
     <hyperlink ref="P3" r:id="rId2" xr:uid="{E30F7852-6389-425A-B287-571FF99532F6}"/>
     <hyperlink ref="O5" r:id="rId3" xr:uid="{D62136F3-CB2F-44C3-B3F1-4721FA1E5EE9}"/>
-    <hyperlink ref="O6" r:id="rId4" xr:uid="{3676D465-641E-4B4D-8677-65A91A2F5628}"/>
-    <hyperlink ref="O7" r:id="rId5" xr:uid="{C150F644-22BC-4D02-802D-BED0E57B013A}"/>
-    <hyperlink ref="O8" r:id="rId6" xr:uid="{99178A6F-2964-4DD4-80DE-C47CB66DDED3}"/>
-    <hyperlink ref="O10" r:id="rId7" xr:uid="{1954C073-6EE4-438F-929C-C507A342B480}"/>
-    <hyperlink ref="O13" r:id="rId8" xr:uid="{6CCCA1FE-ECD2-4689-860F-9ADE3B056949}"/>
-    <hyperlink ref="O11" r:id="rId9" xr:uid="{D35E01C5-0A43-4ACD-BD0C-88FFA33A47B9}"/>
-    <hyperlink ref="O14" r:id="rId10" xr:uid="{A047975B-CA68-4AA6-A365-A332455D0250}"/>
-    <hyperlink ref="O16" r:id="rId11" xr:uid="{E1AFF3FB-1C65-4169-8AC3-97DCAA64B9AF}"/>
-    <hyperlink ref="O18" r:id="rId12" xr:uid="{05E535AF-A000-4512-A566-52195A140416}"/>
-    <hyperlink ref="O19" r:id="rId13" xr:uid="{73FE13B3-6F8A-49A8-897D-09B2CB7F1A5F}"/>
+    <hyperlink ref="O7" r:id="rId4" xr:uid="{3676D465-641E-4B4D-8677-65A91A2F5628}"/>
+    <hyperlink ref="O9" r:id="rId5" xr:uid="{C150F644-22BC-4D02-802D-BED0E57B013A}"/>
+    <hyperlink ref="O11" r:id="rId6" xr:uid="{99178A6F-2964-4DD4-80DE-C47CB66DDED3}"/>
+    <hyperlink ref="O13" r:id="rId7" xr:uid="{1954C073-6EE4-438F-929C-C507A342B480}"/>
+    <hyperlink ref="O15" r:id="rId8" xr:uid="{6CCCA1FE-ECD2-4689-860F-9ADE3B056949}"/>
+    <hyperlink ref="O14" r:id="rId9" xr:uid="{D35E01C5-0A43-4ACD-BD0C-88FFA33A47B9}"/>
+    <hyperlink ref="O16" r:id="rId10" xr:uid="{A047975B-CA68-4AA6-A365-A332455D0250}"/>
+    <hyperlink ref="O19" r:id="rId11" xr:uid="{E1AFF3FB-1C65-4169-8AC3-97DCAA64B9AF}"/>
+    <hyperlink ref="O22" r:id="rId12" xr:uid="{05E535AF-A000-4512-A566-52195A140416}"/>
+    <hyperlink ref="O24" r:id="rId13" xr:uid="{73FE13B3-6F8A-49A8-897D-09B2CB7F1A5F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId14"/>

--- a/ratings.xlsx
+++ b/ratings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\7sher\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85BDAC88-B7D0-4E7E-BDFF-E218E443D147}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED6E9149-4D36-44E0-92FD-DD71A912E270}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1530" yWindow="1560" windowWidth="19470" windowHeight="12765" xr2:uid="{975520F9-B6E9-48FA-9812-89BEC17E316B}"/>
   </bookViews>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="81">
   <si>
     <t>Date</t>
   </si>
@@ -267,6 +267,36 @@
   </si>
   <si>
     <t>FDA regulatory pathway delayed. Still good data. Good potential.</t>
+  </si>
+  <si>
+    <t>ADBE</t>
+  </si>
+  <si>
+    <t>MANH</t>
+  </si>
+  <si>
+    <t>Cheap good long term potential tracking KPIs and management changes to see how genAI changes business model.</t>
+  </si>
+  <si>
+    <t>Cheap solid long term stock</t>
+  </si>
+  <si>
+    <t>ASTS</t>
+  </si>
+  <si>
+    <t>Business model flawed. They have to use spacex rockets to get satellites into space and their biggest competitor is starlink which is part of spacex. They are just at a big disadvantage and constant management lies guidance was way more sattelites years ago but keep getting delayed. Way overvalued, sattelitle internet isnt even that good most places are fully covered by normal telecom. They just can not compete with starlink.</t>
+  </si>
+  <si>
+    <t>CVNA</t>
+  </si>
+  <si>
+    <t>Super expensive, not a good business model. They already almost failed once. The street is over estimating what they can do by a lot.</t>
+  </si>
+  <si>
+    <t>NTLA</t>
+  </si>
+  <si>
+    <t>The market is overestimating the impact of the FDA hold and the patient death. Likely from previous trials it is solid and cheap.</t>
   </si>
 </sst>
 </file>
@@ -687,7 +717,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{054A6B13-8CAC-436C-8123-F4D415EF8DC4}">
-  <dimension ref="A1:V42"/>
+  <dimension ref="A1:V47"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
@@ -887,7 +917,7 @@
         <v>0.46</v>
       </c>
       <c r="M5" s="3">
-        <f>H5/(DATEDIF(C5,$C$42,"d")/365)</f>
+        <f>H5/(DATEDIF(C5,$C$47,"d")/365)</f>
         <v>-9.3799455709869459E-2</v>
       </c>
       <c r="N5" t="s">
@@ -973,7 +1003,7 @@
         <v>0.8</v>
       </c>
       <c r="M7" s="3">
-        <f>H7/(DATEDIF(C7,$C$42,"d")/365)</f>
+        <f>H7/(DATEDIF(C7,$C$47,"d")/365)</f>
         <v>0.98167634841305895</v>
       </c>
       <c r="N7" t="s">
@@ -1050,7 +1080,7 @@
         <v>1.44</v>
       </c>
       <c r="M9" s="3">
-        <f>H9/(DATEDIF(C9,$C$42,"d")/365)</f>
+        <f>H9/(DATEDIF(C9,$C$47,"d")/365)</f>
         <v>-0.41412915340636403</v>
       </c>
       <c r="N9" t="s">
@@ -1067,7 +1097,7 @@
         <v>4.2700000000000002E-2</v>
       </c>
       <c r="V9" s="5">
-        <f>(F9*K9)/MIN(F9:F36)</f>
+        <f>(F9*K9)/MIN(F9:F41)</f>
         <v>-0.4272164397522446</v>
       </c>
     </row>
@@ -1150,7 +1180,7 @@
         <v>4.2700000000000002E-2</v>
       </c>
       <c r="V11" s="5">
-        <f>(F11*K11)/MIN(F11:F30)</f>
+        <f>(F11*K11)/MIN(F11:F35)</f>
         <v>1.3617044791656572</v>
       </c>
     </row>
@@ -1210,7 +1240,7 @@
         <v>1.58</v>
       </c>
       <c r="M13" s="3">
-        <f>H13/(DATEDIF(C13,$C$42,"d")/365)</f>
+        <f>H13/(DATEDIF(C13,$C$47,"d")/365)</f>
         <v>0.70808859190601925</v>
       </c>
       <c r="N13" t="s">
@@ -1227,7 +1257,7 @@
         <v>4.2700000000000002E-2</v>
       </c>
       <c r="V13" s="5">
-        <f>(F13*K13)/MIN(F13:F31)</f>
+        <f>(F13*K13)/MIN(F13:F36)</f>
         <v>0</v>
       </c>
     </row>
@@ -1273,7 +1303,7 @@
         <v>4.2700000000000002E-2</v>
       </c>
       <c r="V14" s="5">
-        <f>(F14*K14)/MIN(F14:F35)</f>
+        <f>(F14*K14)/MIN(F14:F40)</f>
         <v>0</v>
       </c>
     </row>
@@ -1311,7 +1341,7 @@
         <v>0.91</v>
       </c>
       <c r="M15" s="3">
-        <f>H15/(DATEDIF(C15,$C$42,"d")/365)</f>
+        <f>H15/(DATEDIF(C15,$C$47,"d")/365)</f>
         <v>0.38949576041854594</v>
       </c>
       <c r="N15" t="s">
@@ -1328,7 +1358,7 @@
         <v>4.2700000000000002E-2</v>
       </c>
       <c r="V15" s="5">
-        <f>(F15*K15)/MIN(F15:F38)</f>
+        <f>(F15*K15)/MIN(F15:F43)</f>
         <v>0</v>
       </c>
     </row>
@@ -1482,7 +1512,7 @@
         <v>2.52</v>
       </c>
       <c r="M19" s="3">
-        <f>H19/(DATEDIF(C19,$C$42,"d")/365)</f>
+        <f>H19/(DATEDIF(C19,$C$47,"d")/365)</f>
         <v>0.62118330163179492</v>
       </c>
       <c r="N19" t="s">
@@ -1557,7 +1587,7 @@
         <v>3.78</v>
       </c>
       <c r="M21" s="3">
-        <f>H21/(DATEDIF(C21,$C$42,"d")/365)</f>
+        <f>H21/(DATEDIF(C21,$C$47,"d")/365)</f>
         <v>0</v>
       </c>
       <c r="N21" t="s">
@@ -1604,7 +1634,7 @@
         <v>0.87</v>
       </c>
       <c r="M22" s="3">
-        <f>H22/(DATEDIF(C22,$C$42,"d")/365)</f>
+        <f>H22/(DATEDIF(C22,$C$47,"d")/365)</f>
         <v>0.32151257680491541</v>
       </c>
       <c r="N22" t="s">
@@ -1681,7 +1711,7 @@
         <v>0.3</v>
       </c>
       <c r="M24" s="3">
-        <f>H24/(DATEDIF(C24,$C$42,"d")/365)</f>
+        <f>H24/(DATEDIF(C24,$C$47,"d")/365)</f>
         <v>0.24342277468687173</v>
       </c>
       <c r="N24" t="s">
@@ -1757,7 +1787,7 @@
         <v>1.45</v>
       </c>
       <c r="M26" s="3">
-        <f>H26/(DATEDIF(C26,$C$42,"d")/365)</f>
+        <f>H26/(DATEDIF(C26,$C$47,"d")/365)</f>
         <v>-1.1662588806727563</v>
       </c>
       <c r="N26" t="s">
@@ -1797,241 +1827,398 @@
       <c r="R27" s="5"/>
     </row>
     <row r="28" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="I28" s="7" t="s">
+      <c r="B28" t="s">
+        <v>71</v>
+      </c>
+      <c r="C28" s="1">
+        <v>46135</v>
+      </c>
+      <c r="D28" t="s">
+        <v>17</v>
+      </c>
+      <c r="E28" s="2">
+        <v>238.98</v>
+      </c>
+      <c r="F28">
+        <v>3</v>
+      </c>
+      <c r="G28" s="2">
+        <v>238.98</v>
+      </c>
+      <c r="H28" s="3"/>
+      <c r="I28" t="s">
+        <v>73</v>
+      </c>
+      <c r="J28" t="s">
+        <v>45</v>
+      </c>
+      <c r="M28" s="3"/>
+      <c r="O28" s="8"/>
+      <c r="Q28" s="2"/>
+      <c r="R28" s="5"/>
+    </row>
+    <row r="29" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="B29" t="s">
+        <v>72</v>
+      </c>
+      <c r="C29" s="1">
+        <v>46135</v>
+      </c>
+      <c r="D29" t="s">
+        <v>17</v>
+      </c>
+      <c r="E29" s="2">
+        <v>138.32</v>
+      </c>
+      <c r="F29">
+        <v>3</v>
+      </c>
+      <c r="G29" s="2">
+        <v>138.32</v>
+      </c>
+      <c r="H29" s="3"/>
+      <c r="I29" t="s">
+        <v>74</v>
+      </c>
+      <c r="J29" t="s">
+        <v>45</v>
+      </c>
+      <c r="M29" s="3"/>
+      <c r="O29" s="8"/>
+      <c r="Q29" s="2"/>
+      <c r="R29" s="5"/>
+    </row>
+    <row r="30" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="B30" t="s">
+        <v>75</v>
+      </c>
+      <c r="C30" s="1">
+        <v>46135</v>
+      </c>
+      <c r="D30" t="s">
+        <v>18</v>
+      </c>
+      <c r="E30" s="2">
+        <v>78.75</v>
+      </c>
+      <c r="F30">
+        <v>5</v>
+      </c>
+      <c r="G30" s="2">
+        <v>78.75</v>
+      </c>
+      <c r="H30" s="3"/>
+      <c r="I30" t="s">
+        <v>76</v>
+      </c>
+      <c r="J30" t="s">
+        <v>45</v>
+      </c>
+      <c r="M30" s="3"/>
+      <c r="O30" s="8"/>
+      <c r="Q30" s="2"/>
+      <c r="R30" s="5"/>
+    </row>
+    <row r="31" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="B31" t="s">
+        <v>77</v>
+      </c>
+      <c r="C31" s="1">
+        <v>46135</v>
+      </c>
+      <c r="D31" t="s">
+        <v>18</v>
+      </c>
+      <c r="E31" s="2">
+        <v>403.02</v>
+      </c>
+      <c r="F31">
+        <v>3</v>
+      </c>
+      <c r="G31" s="2">
+        <v>403.02</v>
+      </c>
+      <c r="H31" s="3"/>
+      <c r="I31" t="s">
+        <v>78</v>
+      </c>
+      <c r="J31" t="s">
+        <v>45</v>
+      </c>
+      <c r="M31" s="3"/>
+      <c r="O31" s="8"/>
+      <c r="Q31" s="2"/>
+      <c r="R31" s="5"/>
+    </row>
+    <row r="32" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="B32" t="s">
+        <v>79</v>
+      </c>
+      <c r="C32" s="1">
+        <v>46135</v>
+      </c>
+      <c r="D32" t="s">
+        <v>17</v>
+      </c>
+      <c r="E32" s="2">
+        <v>15.87</v>
+      </c>
+      <c r="F32">
+        <v>3</v>
+      </c>
+      <c r="G32" s="2">
+        <v>15.87</v>
+      </c>
+      <c r="H32" s="3"/>
+      <c r="I32" t="s">
+        <v>80</v>
+      </c>
+      <c r="J32" t="s">
+        <v>45</v>
+      </c>
+      <c r="M32" s="3"/>
+      <c r="O32" s="8"/>
+      <c r="Q32" s="2"/>
+      <c r="R32" s="5"/>
+    </row>
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="C33" s="1"/>
+      <c r="E33" s="2"/>
+      <c r="I33" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="J28" s="3">
+      <c r="J33" s="3">
         <f>SUM(J3:J27)/COUNT(J3:J27)</f>
         <v>0.75</v>
       </c>
     </row>
-    <row r="29" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="I29" s="7"/>
-      <c r="J29" s="3"/>
-    </row>
-    <row r="30" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="B30" t="s">
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="I34" s="7"/>
+      <c r="J34" s="3"/>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="B35" t="s">
         <v>26</v>
       </c>
-      <c r="F30" s="2">
+      <c r="F35" s="2">
         <f>AVERAGE(F3:F21)</f>
         <v>4.0999999999999996</v>
       </c>
-      <c r="H30" s="3">
+      <c r="H35" s="3">
         <f>AVERAGE(H3:H26)</f>
         <v>0.22896611277706969</v>
       </c>
-      <c r="K30" s="5">
+      <c r="K35" s="5">
         <f>AVERAGE(K3:K26)</f>
         <v>0.12297159433774532</v>
       </c>
-      <c r="L30" s="2">
+      <c r="L35" s="2">
         <f>AVERAGE(L26,L24,L22,-L19,-L16,L15,L13,-L11,L9,-L7,L5,-L3)</f>
         <v>4.8333333333333339E-2</v>
       </c>
-      <c r="M30" s="3">
+      <c r="M35" s="3">
         <f>AVERAGE(M3:M26)</f>
         <v>2.9261830430937641</v>
       </c>
-      <c r="V30" s="5">
+      <c r="V35" s="5">
         <f>AVERAGE(V3:V15)</f>
         <v>0.26571430959709397</v>
       </c>
     </row>
-    <row r="31" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="H31" s="5"/>
-      <c r="K31" s="5"/>
-      <c r="V31" s="5"/>
-    </row>
-    <row r="32" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="B32" t="s">
+    <row r="36" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="H36" s="5"/>
+      <c r="K36" s="5"/>
+      <c r="V36" s="5"/>
+    </row>
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="B37" t="s">
         <v>18</v>
       </c>
-      <c r="D32">
+      <c r="D37">
         <f>COUNTIF(D3:D21,"SHORT")</f>
         <v>5</v>
       </c>
-      <c r="E32" s="3">
-        <f>D32/$D$34</f>
+      <c r="E37" s="3">
+        <f>D37/$D$39</f>
         <v>0.55555555555555558</v>
       </c>
-      <c r="F32" s="2">
+      <c r="F37" s="2">
         <f>AVERAGE(F16:F21,F11,F7,F3)</f>
         <v>4.166666666666667</v>
       </c>
-      <c r="H32" s="3">
+      <c r="H37" s="3">
         <f>AVERAGE(H16:H21,H11,H7,H3)</f>
         <v>0.53928782354091642</v>
       </c>
-      <c r="J32" s="3">
+      <c r="J37" s="3">
         <f>SUM(J16:J21,J11,J7,J3)/COUNT(J16:J21,J11,J7,J3)</f>
         <v>1</v>
       </c>
-      <c r="K32" s="3"/>
-      <c r="L32" s="2"/>
-      <c r="V32" s="5"/>
-    </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="B33" t="s">
+      <c r="K37" s="3"/>
+      <c r="L37" s="2"/>
+      <c r="V37" s="5"/>
+    </row>
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="B38" t="s">
         <v>17</v>
       </c>
-      <c r="D33">
+      <c r="D38">
         <f>COUNTIF(D3:D21,"LONG")</f>
         <v>4</v>
       </c>
-      <c r="E33" s="3">
-        <f>D33/$D$34</f>
+      <c r="E38" s="3">
+        <f>D38/$D$39</f>
         <v>0.44444444444444442</v>
       </c>
-      <c r="F33" s="2">
+      <c r="F38" s="2">
         <f>AVERAGE(F15,F13,F9,F5)</f>
         <v>4</v>
       </c>
-      <c r="H33" s="3">
+      <c r="H38" s="3">
         <f>AVERAGE(H15,H13,H9,H5,H22,H24,H26)</f>
         <v>7.3077479457506834E-3</v>
       </c>
-      <c r="J33" s="3">
+      <c r="J38" s="3">
         <f>SUM(J15,J13,J9,J5,J22,J24,J26)/COUNT(J15,J13,J9,J5,J22,J24,J26)</f>
         <v>0.5714285714285714</v>
       </c>
-      <c r="K33" s="2"/>
-      <c r="L33" s="2"/>
-      <c r="V33" s="5"/>
-    </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="D34">
-        <f>SUM(D32:D33)</f>
+      <c r="K38" s="2"/>
+      <c r="L38" s="2"/>
+      <c r="V38" s="5"/>
+    </row>
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="D39">
+        <f>SUM(D37:D38)</f>
         <v>9</v>
       </c>
-      <c r="H34" s="5"/>
-      <c r="K34" s="5"/>
-      <c r="V34" s="5"/>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="B35" t="s">
+      <c r="H39" s="5"/>
+      <c r="K39" s="5"/>
+      <c r="V39" s="5"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="B40" t="s">
         <v>4</v>
       </c>
-      <c r="C35" s="1">
+      <c r="C40" s="1">
         <v>45862</v>
       </c>
-      <c r="E35" s="2">
+      <c r="E40" s="2">
         <v>634.41999999999996</v>
       </c>
-      <c r="G35" s="2">
+      <c r="G40" s="2">
         <v>708.45</v>
       </c>
-      <c r="H35" s="3">
-        <f>G35/E35-1</f>
+      <c r="H40" s="3">
+        <f>G40/E40-1</f>
         <v>0.11668925948110109</v>
       </c>
-      <c r="I35" s="3"/>
-      <c r="K35" s="5">
-        <f>H35-($H$36+L35*($H$35-$H$36))</f>
+      <c r="I40" s="3"/>
+      <c r="K40" s="5">
+        <f>H40-($H$41+L40*($H$40-$H$41))</f>
         <v>0</v>
       </c>
-      <c r="L35">
+      <c r="L40">
         <v>1</v>
       </c>
-      <c r="M35" s="3">
-        <f>H35/(DATEDIF(C35,$C$42,"d")/365)</f>
+      <c r="M40" s="3">
+        <f>H40/(DATEDIF(C40,$C$47,"d")/365)</f>
         <v>0.15601311249304725</v>
       </c>
     </row>
-    <row r="36" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="B36" t="s">
+    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="B41" t="s">
         <v>20</v>
       </c>
-      <c r="C36" s="1"/>
-      <c r="H36" s="5">
+      <c r="C41" s="1"/>
+      <c r="H41" s="5">
         <v>4.2999999999999997E-2</v>
       </c>
-      <c r="I36" s="3"/>
-      <c r="K36" s="5">
-        <f>H36-($H$36+L36*($H$35-$H$36))</f>
+      <c r="I41" s="3"/>
+      <c r="K41" s="5">
+        <f>H41-($H$41+L41*($H$40-$H$41))</f>
         <v>0</v>
       </c>
-      <c r="L36">
+      <c r="L41">
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="J37" t="s">
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="J42" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="B38" t="s">
+    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="B43" t="s">
         <v>28</v>
       </c>
-      <c r="J38" s="3">
+      <c r="J43" s="3">
         <f>SUM(J3,J5,J7,J11,J13,J14)/COUNT(J3,J5,J7,J11,J13,J14)</f>
         <v>0.8</v>
       </c>
-      <c r="K38" s="5">
+      <c r="K43" s="5">
         <f>AVERAGE(K3,K5,K7,K11,K13,K14)</f>
         <v>0.42278500028705379</v>
       </c>
-      <c r="L38" s="2">
+      <c r="L43" s="2">
         <f>AVERAGE(L3,L5,L7,L11,L13,L14)</f>
         <v>1.0316666666666667</v>
       </c>
-      <c r="M38" s="3">
+      <c r="M43" s="3">
         <f>AVERAGE(M3,M5,M7,M11,M13,M14)</f>
         <v>7.0879203095733772</v>
       </c>
     </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="B39" t="s">
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="B44" t="s">
         <v>29</v>
       </c>
-      <c r="J39">
+      <c r="J44">
         <f>SUM(J9)/COUNT(J9)</f>
         <v>0</v>
       </c>
-      <c r="K39" s="5">
+      <c r="K44" s="5">
         <f>AVERAGE(K9)</f>
         <v>-0.42721643975224455</v>
       </c>
-      <c r="L39" s="2">
+      <c r="L44" s="2">
         <f>AVERAGE(L9)</f>
         <v>1.44</v>
       </c>
-      <c r="M39" s="3">
+      <c r="M44" s="3">
         <f>AVERAGE(M9)</f>
         <v>-0.41412915340636403</v>
       </c>
     </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="B40" t="s">
+    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="B45" t="s">
         <v>30</v>
       </c>
-      <c r="I40" s="3"/>
-      <c r="J40">
+      <c r="I45" s="3"/>
+      <c r="J45">
         <f>SUM(J15)/COUNT(J15)</f>
         <v>1</v>
       </c>
-      <c r="K40" s="5" t="e">
+      <c r="K45" s="5" t="e">
         <f>AVERAGE(K15)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="L40" s="2">
+      <c r="L45" s="2">
         <f>AVERAGE(L15)</f>
         <v>0.91</v>
       </c>
-      <c r="M40" s="3">
+      <c r="M45" s="3">
         <f>AVERAGE(M15)</f>
         <v>0.38949576041854594</v>
       </c>
     </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="B42" t="s">
+    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="B47" t="s">
         <v>63</v>
       </c>
-      <c r="C42" s="1">
+      <c r="C47" s="1">
         <v>46135</v>
       </c>
-      <c r="K42" s="5"/>
+      <c r="K47" s="5"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/ratings.xlsx
+++ b/ratings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\7sher\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED6E9149-4D36-44E0-92FD-DD71A912E270}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C91DAC2-0C98-49DB-92CD-DAD45EED95EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1530" yWindow="1560" windowWidth="19470" windowHeight="12765" xr2:uid="{975520F9-B6E9-48FA-9812-89BEC17E316B}"/>
+    <workbookView xWindow="6615" yWindow="1665" windowWidth="19830" windowHeight="13680" xr2:uid="{975520F9-B6E9-48FA-9812-89BEC17E316B}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -53,8 +53,30 @@
 </comments>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="87">
   <si>
     <t>Date</t>
   </si>
@@ -191,9 +213,6 @@
     <t>Closed after final clinical trial results released. The data from new patients added was about as bad as it could be but the company proceeded with a phase 3 so the stock didn't completely collapsed. The phase 3 is likely to fail but I recommended closing the position due to limited upside and long time it will take for the phase 3 results to be released and collapse the stock price.</t>
   </si>
   <si>
-    <t>|</t>
-  </si>
-  <si>
     <t>Very stable cheap stock with a significant amount of PP&amp;E even subtracting debt the PP&amp;E is worth more than the market cap. This buisness virtually has no threat and easy to run so assuming any positive return on PP&amp;E the stock is cheap.</t>
   </si>
   <si>
@@ -297,6 +316,27 @@
   </si>
   <si>
     <t>The market is overestimating the impact of the FDA hold and the patient death. Likely from previous trials it is solid and cheap.</t>
+  </si>
+  <si>
+    <t>VIR</t>
+  </si>
+  <si>
+    <t>Undervalued pipeline+platforms</t>
+  </si>
+  <si>
+    <t>Software</t>
+  </si>
+  <si>
+    <t>Supply Chain Management</t>
+  </si>
+  <si>
+    <t>Automotive Resale</t>
+  </si>
+  <si>
+    <t>Satellite Telecom</t>
+  </si>
+  <si>
+    <t>Fintech</t>
   </si>
 </sst>
 </file>
@@ -346,7 +386,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -368,6 +408,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="fill"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -717,7 +760,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{054A6B13-8CAC-436C-8123-F4D415EF8DC4}">
-  <dimension ref="A1:V47"/>
+  <dimension ref="A1:V48"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
@@ -735,7 +778,7 @@
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A1" s="10" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B1" s="1"/>
       <c r="V1" t="s">
@@ -866,11 +909,8 @@
         <v>2.4900000000000002</v>
       </c>
       <c r="H4" s="3"/>
-      <c r="I4" t="s">
+      <c r="I4" s="11" t="s">
         <v>44</v>
-      </c>
-      <c r="J4" t="s">
-        <v>45</v>
       </c>
       <c r="K4" s="5"/>
       <c r="O4" s="6"/>
@@ -903,8 +943,8 @@
         <f>G5/E5-1</f>
         <v>-6.3732232920678422E-2</v>
       </c>
-      <c r="I5" t="s">
-        <v>47</v>
+      <c r="I5" s="11" t="s">
+        <v>46</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -917,7 +957,7 @@
         <v>0.46</v>
       </c>
       <c r="M5" s="3">
-        <f>H5/(DATEDIF(C5,$C$47,"d")/365)</f>
+        <f>H5/(DATEDIF(C5,$C$48,"d")/365)</f>
         <v>-9.3799455709869459E-2</v>
       </c>
       <c r="N5" t="s">
@@ -950,11 +990,8 @@
       </c>
       <c r="G6" s="2"/>
       <c r="H6" s="3"/>
-      <c r="I6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J6" t="s">
-        <v>45</v>
+      <c r="I6" s="11" t="s">
+        <v>63</v>
       </c>
       <c r="K6" s="5"/>
       <c r="M6" s="3"/>
@@ -990,7 +1027,7 @@
         <v>0.66700201207243459</v>
       </c>
       <c r="I7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J7">
         <v>1</v>
@@ -1003,7 +1040,7 @@
         <v>0.8</v>
       </c>
       <c r="M7" s="3">
-        <f>H7/(DATEDIF(C7,$C$47,"d")/365)</f>
+        <f>H7/(DATEDIF(C7,$C$48,"d")/365)</f>
         <v>0.98167634841305895</v>
       </c>
       <c r="N7" t="s">
@@ -1066,8 +1103,8 @@
         <f>G9/E9-1</f>
         <v>-0.28138090423226925</v>
       </c>
-      <c r="I9" t="s">
-        <v>49</v>
+      <c r="I9" s="11" t="s">
+        <v>48</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -1080,11 +1117,11 @@
         <v>1.44</v>
       </c>
       <c r="M9" s="3">
-        <f>H9/(DATEDIF(C9,$C$47,"d")/365)</f>
+        <f>H9/(DATEDIF(C9,$C$48,"d")/365)</f>
         <v>-0.41412915340636403</v>
       </c>
       <c r="N9" t="s">
-        <v>29</v>
+        <v>86</v>
       </c>
       <c r="O9" s="8" t="s">
         <v>37</v>
@@ -1097,7 +1134,7 @@
         <v>4.2700000000000002E-2</v>
       </c>
       <c r="V9" s="5">
-        <f>(F9*K9)/MIN(F9:F41)</f>
+        <f>(F9*K9)/MIN(F9:F42)</f>
         <v>-0.4272164397522446</v>
       </c>
     </row>
@@ -1110,11 +1147,8 @@
       </c>
       <c r="G10" s="2"/>
       <c r="H10" s="3"/>
-      <c r="I10" t="s">
-        <v>65</v>
-      </c>
-      <c r="J10" t="s">
-        <v>45</v>
+      <c r="I10" s="11" t="s">
+        <v>64</v>
       </c>
       <c r="K10" s="5"/>
       <c r="M10" s="3"/>
@@ -1149,8 +1183,8 @@
         <f>(E12/E11-1)*-1</f>
         <v>0.84150943396226419</v>
       </c>
-      <c r="I11" t="s">
-        <v>51</v>
+      <c r="I11" s="11" t="s">
+        <v>50</v>
       </c>
       <c r="J11">
         <v>1</v>
@@ -1180,7 +1214,7 @@
         <v>4.2700000000000002E-2</v>
       </c>
       <c r="V11" s="5">
-        <f>(F11*K11)/MIN(F11:F35)</f>
+        <f>(F11*K11)/MIN(F11:F36)</f>
         <v>1.3617044791656572</v>
       </c>
     </row>
@@ -1196,6 +1230,7 @@
       </c>
       <c r="G12" s="2"/>
       <c r="H12" s="3"/>
+      <c r="I12" s="11"/>
       <c r="K12" s="5"/>
       <c r="M12" s="3"/>
       <c r="O12" s="8"/>
@@ -1229,8 +1264,8 @@
         <f>G13/E13-1</f>
         <v>0.46753246753246747</v>
       </c>
-      <c r="I13" t="s">
-        <v>66</v>
+      <c r="I13" s="11" t="s">
+        <v>65</v>
       </c>
       <c r="J13">
         <v>1</v>
@@ -1240,7 +1275,7 @@
         <v>1.58</v>
       </c>
       <c r="M13" s="3">
-        <f>H13/(DATEDIF(C13,$C$47,"d")/365)</f>
+        <f>H13/(DATEDIF(C13,$C$48,"d")/365)</f>
         <v>0.70808859190601925</v>
       </c>
       <c r="N13" t="s">
@@ -1257,7 +1292,7 @@
         <v>4.2700000000000002E-2</v>
       </c>
       <c r="V13" s="5">
-        <f>(F13*K13)/MIN(F13:F36)</f>
+        <f>(F13*K13)/MIN(F13:F37)</f>
         <v>0</v>
       </c>
     </row>
@@ -1278,11 +1313,8 @@
         <v>22.27</v>
       </c>
       <c r="H14" s="3"/>
-      <c r="I14" t="s">
-        <v>54</v>
-      </c>
-      <c r="J14" t="s">
-        <v>45</v>
+      <c r="I14" s="11" t="s">
+        <v>53</v>
       </c>
       <c r="K14" s="5"/>
       <c r="L14">
@@ -1303,7 +1335,7 @@
         <v>4.2700000000000002E-2</v>
       </c>
       <c r="V14" s="5">
-        <f>(F14*K14)/MIN(F14:F40)</f>
+        <f>(F14*K14)/MIN(F14:F41)</f>
         <v>0</v>
       </c>
     </row>
@@ -1330,8 +1362,8 @@
         <f>G15/E15-1</f>
         <v>0.25717391304347825</v>
       </c>
-      <c r="I15" t="s">
-        <v>46</v>
+      <c r="I15" s="11" t="s">
+        <v>45</v>
       </c>
       <c r="J15">
         <v>1</v>
@@ -1341,7 +1373,7 @@
         <v>0.91</v>
       </c>
       <c r="M15" s="3">
-        <f>H15/(DATEDIF(C15,$C$47,"d")/365)</f>
+        <f>H15/(DATEDIF(C15,$C$48,"d")/365)</f>
         <v>0.38949576041854594</v>
       </c>
       <c r="N15" t="s">
@@ -1358,7 +1390,7 @@
         <v>4.2700000000000002E-2</v>
       </c>
       <c r="V15" s="5">
-        <f>(F15*K15)/MIN(F15:F43)</f>
+        <f>(F15*K15)/MIN(F15:F44)</f>
         <v>0</v>
       </c>
     </row>
@@ -1385,8 +1417,8 @@
         <f>(E18/(AVERAGE(E16:E17))-1)*-1</f>
         <v>0.38433139692708618</v>
       </c>
-      <c r="I16" t="s">
-        <v>52</v>
+      <c r="I16" s="11" t="s">
+        <v>51</v>
       </c>
       <c r="J16">
         <v>1</v>
@@ -1422,7 +1454,7 @@
         <v>45926</v>
       </c>
       <c r="D17" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E17" s="2">
         <v>111.19</v>
@@ -1430,11 +1462,8 @@
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
       <c r="H17" s="3"/>
-      <c r="I17" t="s">
-        <v>61</v>
-      </c>
-      <c r="J17" t="s">
-        <v>45</v>
+      <c r="I17" s="11" t="s">
+        <v>60</v>
       </c>
       <c r="K17" s="5"/>
       <c r="M17" s="3">
@@ -1461,11 +1490,8 @@
       </c>
       <c r="G18" s="2"/>
       <c r="H18" s="3"/>
-      <c r="I18" t="s">
-        <v>67</v>
-      </c>
-      <c r="J18" t="s">
-        <v>45</v>
+      <c r="I18" s="11" t="s">
+        <v>66</v>
       </c>
       <c r="K18" s="5"/>
       <c r="M18" s="3"/>
@@ -1498,8 +1524,8 @@
         <f>(E20/E19-1)*-1</f>
         <v>0.40504555010511556</v>
       </c>
-      <c r="I19" t="s">
-        <v>53</v>
+      <c r="I19" s="11" t="s">
+        <v>52</v>
       </c>
       <c r="J19">
         <v>1</v>
@@ -1512,7 +1538,7 @@
         <v>2.52</v>
       </c>
       <c r="M19" s="3">
-        <f>H19/(DATEDIF(C19,$C$47,"d")/365)</f>
+        <f>H19/(DATEDIF(C19,$C$48,"d")/365)</f>
         <v>0.62118330163179492</v>
       </c>
       <c r="N19" t="s">
@@ -1542,11 +1568,8 @@
       </c>
       <c r="G20" s="2"/>
       <c r="H20" s="3"/>
-      <c r="I20" t="s">
-        <v>67</v>
-      </c>
-      <c r="J20" t="s">
-        <v>45</v>
+      <c r="I20" s="11" t="s">
+        <v>66</v>
       </c>
       <c r="K20" s="5"/>
       <c r="M20" s="3"/>
@@ -1577,17 +1600,14 @@
       <c r="G21" s="2">
         <v>172.47</v>
       </c>
-      <c r="I21" t="s">
-        <v>50</v>
-      </c>
-      <c r="J21" t="s">
-        <v>45</v>
+      <c r="I21" s="11" t="s">
+        <v>49</v>
       </c>
       <c r="L21">
         <v>3.78</v>
       </c>
       <c r="M21" s="3">
-        <f>H21/(DATEDIF(C21,$C$47,"d")/365)</f>
+        <f>H21/(DATEDIF(C21,$C$48,"d")/365)</f>
         <v>0</v>
       </c>
       <c r="N21" t="s">
@@ -1620,8 +1640,8 @@
         <f>E23/E22-1</f>
         <v>0.19731182795698921</v>
       </c>
-      <c r="I22" t="s">
-        <v>55</v>
+      <c r="I22" s="11" t="s">
+        <v>54</v>
       </c>
       <c r="J22">
         <v>1</v>
@@ -1634,7 +1654,7 @@
         <v>0.87</v>
       </c>
       <c r="M22" s="3">
-        <f>H22/(DATEDIF(C22,$C$47,"d")/365)</f>
+        <f>H22/(DATEDIF(C22,$C$48,"d")/365)</f>
         <v>0.32151257680491541</v>
       </c>
       <c r="N22" t="s">
@@ -1661,11 +1681,8 @@
         <v>22.27</v>
       </c>
       <c r="H23" s="3"/>
-      <c r="I23" t="s">
-        <v>68</v>
-      </c>
-      <c r="J23" t="s">
-        <v>45</v>
+      <c r="I23" s="11" t="s">
+        <v>67</v>
       </c>
       <c r="M23" s="3"/>
       <c r="O23" s="8"/>
@@ -1676,7 +1693,7 @@
     </row>
     <row r="24" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B24" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C24" s="1">
         <v>45922</v>
@@ -1697,8 +1714,8 @@
         <f>G24/E24-1</f>
         <v>0.14205219454329776</v>
       </c>
-      <c r="I24" t="s">
-        <v>59</v>
+      <c r="I24" s="11" t="s">
+        <v>58</v>
       </c>
       <c r="J24">
         <v>1</v>
@@ -1711,7 +1728,7 @@
         <v>0.3</v>
       </c>
       <c r="M24" s="3">
-        <f>H24/(DATEDIF(C24,$C$47,"d")/365)</f>
+        <f>H24/(DATEDIF(C24,$C$48,"d")/365)</f>
         <v>0.24342277468687173</v>
       </c>
       <c r="N24" t="s">
@@ -1739,9 +1756,7 @@
       </c>
       <c r="G25" s="2"/>
       <c r="H25" s="3"/>
-      <c r="J25" t="s">
-        <v>45</v>
-      </c>
+      <c r="I25" s="11"/>
       <c r="L25" s="2"/>
       <c r="M25" s="3"/>
       <c r="O25" s="8"/>
@@ -1752,7 +1767,7 @@
     </row>
     <row r="26" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B26" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C26" s="1">
         <v>45926</v>
@@ -1773,8 +1788,8 @@
         <f>G26/E26-1</f>
         <v>-0.66780303030303023</v>
       </c>
-      <c r="I26" t="s">
-        <v>56</v>
+      <c r="I26" s="11" t="s">
+        <v>55</v>
       </c>
       <c r="J26">
         <v>0</v>
@@ -1787,7 +1802,7 @@
         <v>1.45</v>
       </c>
       <c r="M26" s="3">
-        <f>H26/(DATEDIF(C26,$C$47,"d")/365)</f>
+        <f>H26/(DATEDIF(C26,$C$48,"d")/365)</f>
         <v>-1.1662588806727563</v>
       </c>
       <c r="N26" t="s">
@@ -1806,18 +1821,15 @@
         <v>46135</v>
       </c>
       <c r="D27" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E27" s="2">
         <v>17.54</v>
       </c>
       <c r="G27" s="2"/>
       <c r="H27" s="3"/>
-      <c r="I27" t="s">
-        <v>70</v>
-      </c>
-      <c r="J27" t="s">
-        <v>45</v>
+      <c r="I27" s="11" t="s">
+        <v>69</v>
       </c>
       <c r="M27" s="3"/>
       <c r="O27" s="8"/>
@@ -1828,7 +1840,7 @@
     </row>
     <row r="28" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B28" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C28" s="1">
         <v>46135</v>
@@ -1846,20 +1858,27 @@
         <v>238.98</v>
       </c>
       <c r="H28" s="3"/>
-      <c r="I28" t="s">
-        <v>73</v>
-      </c>
-      <c r="J28" t="s">
-        <v>45</v>
+      <c r="I28" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="L28">
+        <v>1.52</v>
       </c>
       <c r="M28" s="3"/>
+      <c r="N28" t="s">
+        <v>82</v>
+      </c>
       <c r="O28" s="8"/>
-      <c r="Q28" s="2"/>
-      <c r="R28" s="5"/>
+      <c r="Q28" s="2">
+        <v>708.45</v>
+      </c>
+      <c r="R28" s="5">
+        <v>4.2999999999999997E-2</v>
+      </c>
     </row>
     <row r="29" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B29" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C29" s="1">
         <v>46135</v>
@@ -1877,20 +1896,27 @@
         <v>138.32</v>
       </c>
       <c r="H29" s="3"/>
-      <c r="I29" t="s">
-        <v>74</v>
-      </c>
-      <c r="J29" t="s">
-        <v>45</v>
+      <c r="I29" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="L29">
+        <v>1.05</v>
       </c>
       <c r="M29" s="3"/>
+      <c r="N29" t="s">
+        <v>83</v>
+      </c>
       <c r="O29" s="8"/>
-      <c r="Q29" s="2"/>
-      <c r="R29" s="5"/>
+      <c r="Q29" s="2">
+        <v>708.45</v>
+      </c>
+      <c r="R29" s="5">
+        <v>4.2999999999999997E-2</v>
+      </c>
     </row>
     <row r="30" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B30" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C30" s="1">
         <v>46135</v>
@@ -1908,20 +1934,27 @@
         <v>78.75</v>
       </c>
       <c r="H30" s="3"/>
-      <c r="I30" t="s">
-        <v>76</v>
-      </c>
-      <c r="J30" t="s">
-        <v>45</v>
+      <c r="I30" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="L30">
+        <v>2.8</v>
       </c>
       <c r="M30" s="3"/>
+      <c r="N30" t="s">
+        <v>85</v>
+      </c>
       <c r="O30" s="8"/>
-      <c r="Q30" s="2"/>
-      <c r="R30" s="5"/>
+      <c r="Q30" s="2">
+        <v>708.45</v>
+      </c>
+      <c r="R30" s="5">
+        <v>4.2999999999999997E-2</v>
+      </c>
     </row>
     <row r="31" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B31" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C31" s="1">
         <v>46135</v>
@@ -1939,20 +1972,27 @@
         <v>403.02</v>
       </c>
       <c r="H31" s="3"/>
-      <c r="I31" t="s">
-        <v>78</v>
-      </c>
-      <c r="J31" t="s">
-        <v>45</v>
+      <c r="I31" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="L31">
+        <v>3.61</v>
       </c>
       <c r="M31" s="3"/>
+      <c r="N31" t="s">
+        <v>84</v>
+      </c>
       <c r="O31" s="8"/>
-      <c r="Q31" s="2"/>
-      <c r="R31" s="5"/>
+      <c r="Q31" s="2">
+        <v>708.45</v>
+      </c>
+      <c r="R31" s="5">
+        <v>4.2999999999999997E-2</v>
+      </c>
     </row>
     <row r="32" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B32" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C32" s="1">
         <v>46135</v>
@@ -1970,255 +2010,304 @@
         <v>15.87</v>
       </c>
       <c r="H32" s="3"/>
-      <c r="I32" t="s">
+      <c r="I32" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="L32">
+        <v>1.99</v>
+      </c>
+      <c r="M32" s="3"/>
+      <c r="N32" t="s">
+        <v>28</v>
+      </c>
+      <c r="O32" s="8"/>
+      <c r="Q32" s="2">
+        <v>708.45</v>
+      </c>
+      <c r="R32" s="5">
+        <v>4.2999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="B33" t="s">
         <v>80</v>
       </c>
-      <c r="J32" t="s">
-        <v>45</v>
-      </c>
-      <c r="M32" s="3"/>
-      <c r="O32" s="8"/>
-      <c r="Q32" s="2"/>
-      <c r="R32" s="5"/>
-    </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="C33" s="1"/>
-      <c r="E33" s="2"/>
-      <c r="I33" s="7" t="s">
+      <c r="C33" s="1">
+        <v>46137</v>
+      </c>
+      <c r="D33" t="s">
+        <v>17</v>
+      </c>
+      <c r="E33" s="2">
+        <v>10.37</v>
+      </c>
+      <c r="F33">
+        <v>3</v>
+      </c>
+      <c r="G33" s="2">
+        <v>10.37</v>
+      </c>
+      <c r="H33" s="3"/>
+      <c r="I33" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="L33">
+        <v>1.71</v>
+      </c>
+      <c r="M33" s="3"/>
+      <c r="N33" t="s">
+        <v>28</v>
+      </c>
+      <c r="O33" s="8"/>
+      <c r="Q33" s="2">
+        <v>713.94</v>
+      </c>
+      <c r="R33" s="5">
+        <v>4.2999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="C34" s="1"/>
+      <c r="E34" s="2"/>
+      <c r="I34" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="J33" s="3">
+      <c r="J34" s="3">
         <f>SUM(J3:J27)/COUNT(J3:J27)</f>
         <v>0.75</v>
       </c>
     </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="I34" s="7"/>
-      <c r="J34" s="3"/>
-    </row>
     <row r="35" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="B35" t="s">
+      <c r="I35" s="7"/>
+      <c r="J35" s="3"/>
+      <c r="L35" t="e" cm="1">
+        <f t="array" ref="L35">SUMPRODUCT(B2:B10, IF(A2:A10="Short",-1,1)) / COUNT(B2:B10)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="36" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="B36" t="s">
         <v>26</v>
       </c>
-      <c r="F35" s="2">
+      <c r="F36" s="2">
         <f>AVERAGE(F3:F21)</f>
         <v>4.0999999999999996</v>
       </c>
-      <c r="H35" s="3">
+      <c r="H36" s="3">
         <f>AVERAGE(H3:H26)</f>
         <v>0.22896611277706969</v>
       </c>
-      <c r="K35" s="5">
+      <c r="K36" s="5">
         <f>AVERAGE(K3:K26)</f>
         <v>0.12297159433774532</v>
       </c>
-      <c r="L35" s="2">
-        <f>AVERAGE(L26,L24,L22,-L19,-L16,L15,L13,-L11,L9,-L7,L5,-L3)</f>
-        <v>4.8333333333333339E-2</v>
-      </c>
-      <c r="M35" s="3">
+      <c r="L36" s="2">
+        <f>(SUM(L26,L24,L22,L15,L13,L9,L5,L29,L28,L32,L33)-SUM(L19,L16,L11,L7,L3,L30,L31))/18</f>
+        <v>2.4444444444444515E-2</v>
+      </c>
+      <c r="M36" s="3">
         <f>AVERAGE(M3:M26)</f>
         <v>2.9261830430937641</v>
       </c>
-      <c r="V35" s="5">
+      <c r="V36" s="5">
         <f>AVERAGE(V3:V15)</f>
         <v>0.26571430959709397</v>
       </c>
     </row>
-    <row r="36" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="H36" s="5"/>
-      <c r="K36" s="5"/>
-      <c r="V36" s="5"/>
-    </row>
     <row r="37" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="B37" t="s">
+      <c r="H37" s="5"/>
+      <c r="K37" s="5"/>
+      <c r="V37" s="5"/>
+    </row>
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="B38" t="s">
         <v>18</v>
       </c>
-      <c r="D37">
+      <c r="D38">
         <f>COUNTIF(D3:D21,"SHORT")</f>
         <v>5</v>
       </c>
-      <c r="E37" s="3">
-        <f>D37/$D$39</f>
+      <c r="E38" s="3">
+        <f>D38/$D$40</f>
         <v>0.55555555555555558</v>
       </c>
-      <c r="F37" s="2">
+      <c r="F38" s="2">
         <f>AVERAGE(F16:F21,F11,F7,F3)</f>
         <v>4.166666666666667</v>
       </c>
-      <c r="H37" s="3">
+      <c r="H38" s="3">
         <f>AVERAGE(H16:H21,H11,H7,H3)</f>
         <v>0.53928782354091642</v>
       </c>
-      <c r="J37" s="3">
+      <c r="J38" s="3">
         <f>SUM(J16:J21,J11,J7,J3)/COUNT(J16:J21,J11,J7,J3)</f>
         <v>1</v>
       </c>
-      <c r="K37" s="3"/>
-      <c r="L37" s="2"/>
-      <c r="V37" s="5"/>
-    </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="B38" t="s">
+      <c r="K38" s="3"/>
+      <c r="L38" s="2"/>
+      <c r="V38" s="5"/>
+    </row>
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="B39" t="s">
         <v>17</v>
       </c>
-      <c r="D38">
+      <c r="D39">
         <f>COUNTIF(D3:D21,"LONG")</f>
         <v>4</v>
       </c>
-      <c r="E38" s="3">
-        <f>D38/$D$39</f>
+      <c r="E39" s="3">
+        <f>D39/$D$40</f>
         <v>0.44444444444444442</v>
       </c>
-      <c r="F38" s="2">
+      <c r="F39" s="2">
         <f>AVERAGE(F15,F13,F9,F5)</f>
         <v>4</v>
       </c>
-      <c r="H38" s="3">
+      <c r="H39" s="3">
         <f>AVERAGE(H15,H13,H9,H5,H22,H24,H26)</f>
         <v>7.3077479457506834E-3</v>
       </c>
-      <c r="J38" s="3">
+      <c r="J39" s="3">
         <f>SUM(J15,J13,J9,J5,J22,J24,J26)/COUNT(J15,J13,J9,J5,J22,J24,J26)</f>
         <v>0.5714285714285714</v>
       </c>
-      <c r="K38" s="2"/>
-      <c r="L38" s="2"/>
-      <c r="V38" s="5"/>
-    </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="D39">
-        <f>SUM(D37:D38)</f>
+      <c r="K39" s="2"/>
+      <c r="L39" s="2"/>
+      <c r="V39" s="5"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="D40">
+        <f>SUM(D38:D39)</f>
         <v>9</v>
       </c>
-      <c r="H39" s="5"/>
-      <c r="K39" s="5"/>
-      <c r="V39" s="5"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="B40" t="s">
-        <v>4</v>
-      </c>
-      <c r="C40" s="1">
-        <v>45862</v>
-      </c>
-      <c r="E40" s="2">
-        <v>634.41999999999996</v>
-      </c>
-      <c r="G40" s="2">
-        <v>708.45</v>
-      </c>
-      <c r="H40" s="3">
-        <f>G40/E40-1</f>
-        <v>0.11668925948110109</v>
-      </c>
-      <c r="I40" s="3"/>
-      <c r="K40" s="5">
-        <f>H40-($H$41+L40*($H$40-$H$41))</f>
-        <v>0</v>
-      </c>
-      <c r="L40">
-        <v>1</v>
-      </c>
-      <c r="M40" s="3">
-        <f>H40/(DATEDIF(C40,$C$47,"d")/365)</f>
-        <v>0.15601311249304725</v>
-      </c>
+      <c r="H40" s="5"/>
+      <c r="K40" s="5"/>
+      <c r="V40" s="5"/>
     </row>
     <row r="41" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B41" t="s">
-        <v>20</v>
-      </c>
-      <c r="C41" s="1"/>
-      <c r="H41" s="5">
-        <v>4.2999999999999997E-2</v>
+        <v>4</v>
+      </c>
+      <c r="C41" s="1">
+        <v>45862</v>
+      </c>
+      <c r="E41" s="2">
+        <v>634.41999999999996</v>
+      </c>
+      <c r="G41" s="2">
+        <v>708.45</v>
+      </c>
+      <c r="H41" s="3">
+        <f>G41/E41-1</f>
+        <v>0.11668925948110109</v>
       </c>
       <c r="I41" s="3"/>
       <c r="K41" s="5">
-        <f>H41-($H$41+L41*($H$40-$H$41))</f>
+        <f>H41-($H$42+L41*($H$41-$H$42))</f>
         <v>0</v>
       </c>
       <c r="L41">
+        <v>1</v>
+      </c>
+      <c r="M41" s="3">
+        <f>H41/(DATEDIF(C41,$C$48,"d")/365)</f>
+        <v>0.15601311249304725</v>
+      </c>
+    </row>
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="B42" t="s">
+        <v>20</v>
+      </c>
+      <c r="C42" s="1"/>
+      <c r="H42" s="5">
+        <v>4.2999999999999997E-2</v>
+      </c>
+      <c r="I42" s="3"/>
+      <c r="K42" s="5">
+        <f>H42-($H$42+L42*($H$41-$H$42))</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="J42" t="s">
+      <c r="L42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="J43" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="B43" t="s">
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="B44" t="s">
         <v>28</v>
       </c>
-      <c r="J43" s="3">
+      <c r="J44" s="3">
         <f>SUM(J3,J5,J7,J11,J13,J14)/COUNT(J3,J5,J7,J11,J13,J14)</f>
         <v>0.8</v>
       </c>
-      <c r="K43" s="5">
+      <c r="K44" s="5">
         <f>AVERAGE(K3,K5,K7,K11,K13,K14)</f>
         <v>0.42278500028705379</v>
       </c>
-      <c r="L43" s="2">
+      <c r="L44" s="2">
         <f>AVERAGE(L3,L5,L7,L11,L13,L14)</f>
         <v>1.0316666666666667</v>
       </c>
-      <c r="M43" s="3">
+      <c r="M44" s="3">
         <f>AVERAGE(M3,M5,M7,M11,M13,M14)</f>
         <v>7.0879203095733772</v>
       </c>
     </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="B44" t="s">
+    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="B45" t="s">
         <v>29</v>
       </c>
-      <c r="J44">
+      <c r="J45">
         <f>SUM(J9)/COUNT(J9)</f>
         <v>0</v>
       </c>
-      <c r="K44" s="5">
+      <c r="K45" s="5">
         <f>AVERAGE(K9)</f>
         <v>-0.42721643975224455</v>
       </c>
-      <c r="L44" s="2">
+      <c r="L45" s="2">
         <f>AVERAGE(L9)</f>
         <v>1.44</v>
       </c>
-      <c r="M44" s="3">
+      <c r="M45" s="3">
         <f>AVERAGE(M9)</f>
         <v>-0.41412915340636403</v>
       </c>
     </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="B45" t="s">
+    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="B46" t="s">
         <v>30</v>
       </c>
-      <c r="I45" s="3"/>
-      <c r="J45">
+      <c r="I46" s="3"/>
+      <c r="J46">
         <f>SUM(J15)/COUNT(J15)</f>
         <v>1</v>
       </c>
-      <c r="K45" s="5" t="e">
+      <c r="K46" s="5" t="e">
         <f>AVERAGE(K15)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="L45" s="2">
+      <c r="L46" s="2">
         <f>AVERAGE(L15)</f>
         <v>0.91</v>
       </c>
-      <c r="M45" s="3">
+      <c r="M46" s="3">
         <f>AVERAGE(M15)</f>
         <v>0.38949576041854594</v>
       </c>
     </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="B47" t="s">
-        <v>63</v>
-      </c>
-      <c r="C47" s="1">
+    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="B48" t="s">
+        <v>62</v>
+      </c>
+      <c r="C48" s="1">
         <v>46135</v>
       </c>
-      <c r="K47" s="5"/>
+      <c r="K48" s="5"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/ratings.xlsx
+++ b/ratings.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\7sher\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C91DAC2-0C98-49DB-92CD-DAD45EED95EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84F39A55-7E81-44E0-8ABC-05D75713683B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6615" yWindow="1665" windowWidth="19830" windowHeight="13680" xr2:uid="{975520F9-B6E9-48FA-9812-89BEC17E316B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{975520F9-B6E9-48FA-9812-89BEC17E316B}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -76,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="97">
   <si>
     <t>Date</t>
   </si>
@@ -165,9 +165,6 @@
     <t>Biopharma</t>
   </si>
   <si>
-    <t>Tech</t>
-  </si>
-  <si>
     <t>Energy</t>
   </si>
   <si>
@@ -261,9 +258,6 @@
     <t>Lots of market exposure to movement but long term this is likely to drop and I would add here to the short at this very high price as long as your position isn't too large</t>
   </si>
   <si>
-    <t>update: 4/23/2026</t>
-  </si>
-  <si>
     <t>Current Date</t>
   </si>
   <si>
@@ -337,6 +331,42 @@
   </si>
   <si>
     <t>Fintech</t>
+  </si>
+  <si>
+    <t>update: 8/27/2026</t>
+  </si>
+  <si>
+    <t>Long term hold</t>
+  </si>
+  <si>
+    <t>Cheap but in transitional phase depends on next management which were still waiting on wouldn’t add just hold until management is clear on their plan in next fiscal year</t>
+  </si>
+  <si>
+    <t>Thesis proven right long term hold</t>
+  </si>
+  <si>
+    <t>Good short for hedge and high beta</t>
+  </si>
+  <si>
+    <t>NRG</t>
+  </si>
+  <si>
+    <t>Large demand regulatory is likely to be loose and growth looks good cheap</t>
+  </si>
+  <si>
+    <t>COGT</t>
+  </si>
+  <si>
+    <t>ARQT</t>
+  </si>
+  <si>
+    <t>SNDX</t>
+  </si>
+  <si>
+    <t>don’t really like original reason of shorting based on just valuation and not something guaranteed to force the stock down</t>
+  </si>
+  <si>
+    <t>Q426 Q127 data readouts good Ph2 likely Ph3 success implied success ~55%</t>
   </si>
 </sst>
 </file>
@@ -760,7 +790,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{054A6B13-8CAC-436C-8123-F4D415EF8DC4}">
-  <dimension ref="A1:V48"/>
+  <dimension ref="A1:V54"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
@@ -778,7 +808,7 @@
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A1" s="10" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="B1" s="1"/>
       <c r="V1" t="s">
@@ -820,22 +850,22 @@
         <v>21</v>
       </c>
       <c r="M2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="N2" t="s">
         <v>27</v>
       </c>
       <c r="O2" t="s">
+        <v>34</v>
+      </c>
+      <c r="P2" t="s">
         <v>35</v>
       </c>
-      <c r="P2" t="s">
-        <v>36</v>
-      </c>
       <c r="Q2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="R2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="V2" t="s">
         <v>24</v>
@@ -868,8 +898,8 @@
         <v>1</v>
       </c>
       <c r="K3" s="5">
-        <f>H3-(R3+L3*((Q4/Q3)-1)-R3)</f>
-        <v>0.39845362807704293</v>
+        <f>H3-R3-L3*((Q4/Q3-1)-R3)</f>
+        <v>0.42151162807704295</v>
       </c>
       <c r="L3">
         <v>1.54</v>
@@ -882,10 +912,10 @@
         <v>28</v>
       </c>
       <c r="O3" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P3" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q3" s="2">
         <v>634.41999999999996</v>
@@ -894,8 +924,8 @@
         <v>4.2700000000000002E-2</v>
       </c>
       <c r="V3" s="5">
-        <f>(F3*K3)/MIN(F3:F15)</f>
-        <v>0.39845362807704293</v>
+        <f>(F3*K3)/MIN(F3:F16)</f>
+        <v>0.42151162807704295</v>
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.2">
@@ -903,14 +933,14 @@
         <v>45868</v>
       </c>
       <c r="D4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E4">
         <v>2.4900000000000002</v>
       </c>
       <c r="H4" s="3"/>
       <c r="I4" s="11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K4" s="5"/>
       <c r="O4" s="6"/>
@@ -944,27 +974,27 @@
         <v>-6.3732232920678422E-2</v>
       </c>
       <c r="I5" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J5">
         <v>0</v>
       </c>
       <c r="K5" s="5">
-        <f>H5-(R5+L5*((Q6/Q5)-1)-R5)</f>
-        <v>-0.11031858454511499</v>
+        <f>H5-R5-L5*((Q6/Q5-1)-R5)</f>
+        <v>-0.13337658454511497</v>
       </c>
       <c r="L5">
         <v>0.46</v>
       </c>
       <c r="M5" s="3">
-        <f>H5/(DATEDIF(C5,$C$48,"d")/365)</f>
-        <v>-9.3799455709869459E-2</v>
+        <f>H5/(DATEDIF(C5,$C$54,"d")/365)</f>
+        <v>-6.2198569561624666E-2</v>
       </c>
       <c r="N5" t="s">
         <v>28</v>
       </c>
       <c r="O5" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P5" s="9"/>
       <c r="Q5" s="2">
@@ -974,8 +1004,8 @@
         <v>4.2700000000000002E-2</v>
       </c>
       <c r="V5" s="5">
-        <f>(F5*K5)/MIN(F5:F15)</f>
-        <v>-0.18386430757519165</v>
+        <f>(F5*K5)/MIN(F5:F16)</f>
+        <v>-0.22229430757519161</v>
       </c>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.2">
@@ -983,7 +1013,7 @@
         <v>46135</v>
       </c>
       <c r="D6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E6">
         <v>20.420000000000002</v>
@@ -991,7 +1021,7 @@
       <c r="G6" s="2"/>
       <c r="H6" s="3"/>
       <c r="I6" s="11" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="K6" s="5"/>
       <c r="M6" s="3"/>
@@ -1027,27 +1057,27 @@
         <v>0.66700201207243459</v>
       </c>
       <c r="I7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J7">
         <v>1</v>
       </c>
       <c r="K7" s="5">
-        <f>H7-(R7+L7*((Q8/Q7)-1)-R7)</f>
-        <v>0.58598227011689275</v>
+        <f>H7-R7-L7*((Q8/Q7-1)-R7)</f>
+        <v>0.57744227011689275</v>
       </c>
       <c r="L7" s="2">
         <v>0.8</v>
       </c>
       <c r="M7" s="3">
-        <f>H7/(DATEDIF(C7,$C$48,"d")/365)</f>
-        <v>0.98167634841305895</v>
+        <f>H7/(DATEDIF(C7,$C$54,"d")/365)</f>
+        <v>0.6509511615145418</v>
       </c>
       <c r="N7" t="s">
         <v>28</v>
       </c>
       <c r="O7" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P7" s="9"/>
       <c r="Q7" s="2">
@@ -1057,8 +1087,8 @@
         <v>4.2700000000000002E-2</v>
       </c>
       <c r="V7" s="5">
-        <f>(F7*K7)/MIN(F7:F21)</f>
-        <v>0.97663711686148791</v>
+        <f>(F7*K7)/MIN(F7:F23)</f>
+        <v>0.96240378352815459</v>
       </c>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.2">
@@ -1066,7 +1096,7 @@
         <v>46135</v>
       </c>
       <c r="D8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H8" s="3"/>
       <c r="K8" s="5"/>
@@ -1104,27 +1134,27 @@
         <v>-0.28138090423226925</v>
       </c>
       <c r="I9" s="11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J9">
         <v>0</v>
       </c>
       <c r="K9" s="5">
-        <f>H9-(R9+L9*((Q10/Q9)-1)-R9)</f>
-        <v>-0.42721643975224455</v>
+        <f>H9-R9-L9*((Q10/Q9-1)-R9)</f>
+        <v>-0.40842843975224458</v>
       </c>
       <c r="L9">
         <v>1.44</v>
       </c>
       <c r="M9" s="3">
-        <f>H9/(DATEDIF(C9,$C$48,"d")/365)</f>
-        <v>-0.41412915340636403</v>
+        <f>H9/(DATEDIF(C9,$C$54,"d")/365)</f>
+        <v>-0.27460970600208096</v>
       </c>
       <c r="N9" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="O9" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P9" s="9"/>
       <c r="Q9" s="2">
@@ -1134,8 +1164,8 @@
         <v>4.2700000000000002E-2</v>
       </c>
       <c r="V9" s="5">
-        <f>(F9*K9)/MIN(F9:F42)</f>
-        <v>-0.4272164397522446</v>
+        <f>(F9*K9)/MIN(F9:F52)</f>
+        <v>-0.40842843975224458</v>
       </c>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.2">
@@ -1143,12 +1173,12 @@
         <v>46135</v>
       </c>
       <c r="D10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G10" s="2"/>
       <c r="H10" s="3"/>
       <c r="I10" s="11" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="K10" s="5"/>
       <c r="M10" s="3"/>
@@ -1184,14 +1214,14 @@
         <v>0.84150943396226419</v>
       </c>
       <c r="I11" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J11">
         <v>1</v>
       </c>
       <c r="K11" s="5">
-        <f>H11-(R11+L11*((Q12/Q11)-1)-R11)</f>
-        <v>0.81702268749939444</v>
+        <f>H11-R11-L11*((Q12/Q11-1)-R11)</f>
+        <v>0.81488768749939444</v>
       </c>
       <c r="L11">
         <v>0.95</v>
@@ -1204,7 +1234,7 @@
         <v>28</v>
       </c>
       <c r="O11" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P11" s="9"/>
       <c r="Q11" s="2">
@@ -1214,8 +1244,8 @@
         <v>4.2700000000000002E-2</v>
       </c>
       <c r="V11" s="5">
-        <f>(F11*K11)/MIN(F11:F36)</f>
-        <v>1.3617044791656572</v>
+        <f>(F11*K11)/MIN(F11:F49)</f>
+        <v>1.3581461458323243</v>
       </c>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.2">
@@ -1223,7 +1253,7 @@
         <v>45926</v>
       </c>
       <c r="D12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E12" s="2">
         <v>0.84</v>
@@ -1258,31 +1288,34 @@
         <v>3</v>
       </c>
       <c r="G13" s="2">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H13" s="3">
         <f>G13/E13-1</f>
-        <v>0.46753246753246747</v>
+        <v>0.49350649350649345</v>
       </c>
       <c r="I13" s="11" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="J13">
         <v>1</v>
       </c>
-      <c r="K13" s="5"/>
+      <c r="K13" s="5">
+        <f>H13-R13-L13*((Q14/Q13-1)-R13)</f>
+        <v>0.20464321898783883</v>
+      </c>
       <c r="L13">
         <v>1.58</v>
       </c>
       <c r="M13" s="3">
-        <f>H13/(DATEDIF(C13,$C$48,"d")/365)</f>
-        <v>0.70808859190601925</v>
+        <f>H13/(DATEDIF(C13,$C$54,"d")/365)</f>
+        <v>0.49081708482253439</v>
       </c>
       <c r="N13" t="s">
         <v>28</v>
       </c>
       <c r="O13" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P13" s="9"/>
       <c r="Q13" s="2">
@@ -1292,95 +1325,63 @@
         <v>4.2700000000000002E-2</v>
       </c>
       <c r="V13" s="5">
-        <f>(F13*K13)/MIN(F13:F37)</f>
-        <v>0</v>
+        <f>(F13*K13)/MIN(F13:F49)</f>
+        <v>0.2046432189878388</v>
       </c>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B14" t="s">
-        <v>8</v>
-      </c>
       <c r="C14" s="1">
-        <v>45894</v>
+        <v>46261</v>
       </c>
       <c r="D14" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="E14" s="2">
-        <v>26</v>
-      </c>
-      <c r="G14" s="2">
-        <v>22.27</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="G14" s="2"/>
       <c r="H14" s="3"/>
-      <c r="I14" s="11" t="s">
-        <v>53</v>
-      </c>
+      <c r="I14" s="11"/>
       <c r="K14" s="5"/>
-      <c r="L14">
-        <v>0.86</v>
-      </c>
       <c r="M14" s="3"/>
-      <c r="N14" t="s">
-        <v>28</v>
-      </c>
-      <c r="O14" s="8" t="s">
-        <v>37</v>
-      </c>
+      <c r="O14" s="8"/>
       <c r="P14" s="9"/>
       <c r="Q14" s="2">
-        <v>642.47</v>
-      </c>
-      <c r="R14" s="5">
-        <v>4.2700000000000002E-2</v>
-      </c>
-      <c r="V14" s="5">
-        <f>(F14*K14)/MIN(F14:F41)</f>
-        <v>0</v>
-      </c>
+        <v>770</v>
+      </c>
+      <c r="R14" s="5"/>
+      <c r="V14" s="5"/>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B15" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C15" s="1">
         <v>45894</v>
       </c>
       <c r="D15" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="E15" s="2">
-        <v>46</v>
-      </c>
-      <c r="F15">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="G15" s="2">
-        <v>57.83</v>
-      </c>
-      <c r="H15" s="3">
-        <f>G15/E15-1</f>
-        <v>0.25717391304347825</v>
-      </c>
+        <v>22.27</v>
+      </c>
+      <c r="H15" s="3"/>
       <c r="I15" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="J15">
-        <v>1</v>
+        <v>52</v>
       </c>
       <c r="K15" s="5"/>
       <c r="L15">
-        <v>0.91</v>
-      </c>
-      <c r="M15" s="3">
-        <f>H15/(DATEDIF(C15,$C$48,"d")/365)</f>
-        <v>0.38949576041854594</v>
-      </c>
+        <v>0.86</v>
+      </c>
+      <c r="M15" s="3"/>
       <c r="N15" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="O15" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P15" s="9"/>
       <c r="Q15" s="2">
@@ -1390,374 +1391,381 @@
         <v>4.2700000000000002E-2</v>
       </c>
       <c r="V15" s="5">
-        <f>(F15*K15)/MIN(F15:F44)</f>
+        <f>(F15*K15)/MIN(F15:F51)</f>
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B16" t="s">
-        <v>39</v>
+        <v>7</v>
       </c>
       <c r="C16" s="1">
-        <v>45897</v>
+        <v>45894</v>
       </c>
       <c r="D16" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E16" s="2">
-        <v>73</v>
+        <v>46</v>
       </c>
       <c r="F16">
         <v>5</v>
       </c>
       <c r="G16" s="2">
-        <v>76.459999999999994</v>
+        <v>59</v>
       </c>
       <c r="H16" s="3">
-        <f>(E18/(AVERAGE(E16:E17))-1)*-1</f>
-        <v>0.38433139692708618</v>
+        <f>G16/E16-1</f>
+        <v>0.28260869565217384</v>
       </c>
       <c r="I16" s="11" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="J16">
         <v>1</v>
       </c>
       <c r="K16" s="5">
-        <f>H16-(R16+L16*((Q17/Q16)-1)-R16)</f>
-        <v>0.32544577096108923</v>
+        <f>H16-R16-L16*((Q17/Q16-1)-R16)</f>
+        <v>9.8131113492695543E-2</v>
       </c>
       <c r="L16">
-        <v>0.62</v>
+        <v>0.91</v>
       </c>
       <c r="M16" s="3">
-        <f>H16/(DATEDIF(C16,C17,"d")/365)</f>
-        <v>4.8372744785650497</v>
+        <f>H16/(DATEDIF(C16,$C$54,"d")/365)</f>
+        <v>0.28106859376851079</v>
       </c>
       <c r="N16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O16" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P16" s="9"/>
       <c r="Q16" s="2">
-        <v>647</v>
+        <v>642.47</v>
       </c>
       <c r="R16" s="5">
-        <v>4.2299999999999997E-2</v>
-      </c>
-      <c r="V16" s="5"/>
+        <v>4.2700000000000002E-2</v>
+      </c>
+      <c r="V16" s="5">
+        <f>(F16*K16)/MIN(F16:F52)</f>
+        <v>0.16355185582115925</v>
+      </c>
     </row>
     <row r="17" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C17" s="1">
-        <v>45926</v>
+        <v>46261</v>
       </c>
       <c r="D17" t="s">
+        <v>66</v>
+      </c>
+      <c r="E17" s="2">
         <v>59</v>
       </c>
-      <c r="E17" s="2">
-        <v>111.19</v>
-      </c>
-      <c r="F17" s="2"/>
       <c r="G17" s="2"/>
       <c r="H17" s="3"/>
-      <c r="I17" s="11" t="s">
-        <v>60</v>
-      </c>
+      <c r="I17" s="11"/>
       <c r="K17" s="5"/>
-      <c r="M17" s="3">
-        <f>H16/(DATEDIF(C16,C18,"d")/365)</f>
-        <v>0.69446019741775478</v>
-      </c>
+      <c r="M17" s="3"/>
       <c r="O17" s="8"/>
       <c r="P17" s="9"/>
       <c r="Q17" s="2">
-        <v>708.45</v>
+        <v>770</v>
       </c>
       <c r="R17" s="5"/>
       <c r="V17" s="5"/>
     </row>
     <row r="18" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="B18" t="s">
+        <v>38</v>
+      </c>
       <c r="C18" s="1">
-        <v>46099</v>
+        <v>45897</v>
       </c>
       <c r="D18" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="E18" s="2">
-        <v>56.7</v>
-      </c>
-      <c r="G18" s="2"/>
-      <c r="H18" s="3"/>
+        <v>73</v>
+      </c>
+      <c r="F18">
+        <v>5</v>
+      </c>
+      <c r="G18" s="2">
+        <v>76.459999999999994</v>
+      </c>
+      <c r="H18" s="3">
+        <f>(E20/(AVERAGE(E18:E19))-1)*-1</f>
+        <v>0.38433139692708618</v>
+      </c>
       <c r="I18" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="K18" s="5"/>
-      <c r="M18" s="3"/>
-      <c r="O18" s="8"/>
+        <v>50</v>
+      </c>
+      <c r="J18">
+        <v>1</v>
+      </c>
+      <c r="K18" s="5">
+        <f>H18-R18-L18*((Q19/Q18-1)-R18)</f>
+        <v>0.30937177096108925</v>
+      </c>
+      <c r="L18">
+        <v>0.62</v>
+      </c>
+      <c r="M18" s="3">
+        <f>H18/(DATEDIF(C18,C19,"d")/365)</f>
+        <v>4.8372744785650497</v>
+      </c>
+      <c r="N18" t="s">
+        <v>29</v>
+      </c>
+      <c r="O18" s="8" t="s">
+        <v>36</v>
+      </c>
       <c r="P18" s="9"/>
-      <c r="Q18" s="2"/>
-      <c r="R18" s="5"/>
+      <c r="Q18" s="2">
+        <v>647</v>
+      </c>
+      <c r="R18" s="5">
+        <v>4.2299999999999997E-2</v>
+      </c>
       <c r="V18" s="5"/>
     </row>
     <row r="19" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="B19" t="s">
-        <v>40</v>
-      </c>
       <c r="C19" s="1">
-        <v>45897</v>
+        <v>45926</v>
       </c>
       <c r="D19" t="s">
-        <v>18</v>
+        <v>58</v>
       </c>
       <c r="E19" s="2">
-        <v>14.27</v>
-      </c>
-      <c r="F19">
-        <v>3</v>
-      </c>
-      <c r="G19" s="2">
-        <v>8.49</v>
-      </c>
-      <c r="H19" s="3">
-        <f>(E20/E19-1)*-1</f>
-        <v>0.40504555010511556</v>
-      </c>
+        <v>111.19</v>
+      </c>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="3"/>
       <c r="I19" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="J19">
-        <v>1</v>
-      </c>
-      <c r="K19" s="5">
-        <f>H19-(R19+L19*((Q20/Q19)-1)-R19)</f>
-        <v>0.16570397359816025</v>
-      </c>
-      <c r="L19">
-        <v>2.52</v>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="K19" s="5"/>
       <c r="M19" s="3">
-        <f>H19/(DATEDIF(C19,$C$48,"d")/365)</f>
-        <v>0.62118330163179492</v>
-      </c>
-      <c r="N19" t="s">
-        <v>43</v>
-      </c>
-      <c r="O19" s="8" t="s">
-        <v>37</v>
-      </c>
+        <f>H18/(DATEDIF(C18,C20,"d")/365)</f>
+        <v>0.69446019741775478</v>
+      </c>
+      <c r="O19" s="8"/>
       <c r="P19" s="9"/>
       <c r="Q19" s="2">
-        <v>647</v>
-      </c>
-      <c r="R19" s="5">
-        <v>4.2299999999999997E-2</v>
-      </c>
+        <v>708.45</v>
+      </c>
+      <c r="R19" s="5"/>
       <c r="V19" s="5"/>
     </row>
     <row r="20" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C20" s="1">
-        <v>46135</v>
+        <v>46099</v>
       </c>
       <c r="D20" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E20" s="2">
-        <v>8.49</v>
+        <v>56.7</v>
       </c>
       <c r="G20" s="2"/>
       <c r="H20" s="3"/>
       <c r="I20" s="11" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="K20" s="5"/>
       <c r="M20" s="3"/>
       <c r="O20" s="8"/>
       <c r="P20" s="9"/>
-      <c r="Q20" s="2">
-        <v>708.45</v>
-      </c>
+      <c r="Q20" s="2"/>
       <c r="R20" s="5"/>
       <c r="V20" s="5"/>
     </row>
     <row r="21" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B21" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C21" s="1">
         <v>45897</v>
       </c>
       <c r="D21" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E21" s="2">
-        <v>338.84</v>
+        <v>14.27</v>
       </c>
       <c r="F21">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G21" s="2">
-        <v>172.47</v>
+        <v>8.49</v>
+      </c>
+      <c r="H21" s="3">
+        <f>(E22/E21-1)*-1</f>
+        <v>0.40504555010511556</v>
       </c>
       <c r="I21" s="11" t="s">
-        <v>49</v>
+        <v>51</v>
+      </c>
+      <c r="J21">
+        <v>1</v>
+      </c>
+      <c r="K21" s="5">
+        <f>H21-R21-L21*((Q22/Q21-1)-R21)</f>
+        <v>0.22999997359816024</v>
       </c>
       <c r="L21">
-        <v>3.78</v>
+        <v>2.52</v>
       </c>
       <c r="M21" s="3">
-        <f>H21/(DATEDIF(C21,$C$48,"d")/365)</f>
-        <v>0</v>
+        <f>H21/(DATEDIF(C21,$C$54,"d")/365)</f>
+        <v>0.40615831260540436</v>
       </c>
       <c r="N21" t="s">
         <v>42</v>
       </c>
+      <c r="O21" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="P21" s="9"/>
       <c r="Q21" s="2">
         <v>647</v>
       </c>
       <c r="R21" s="5">
         <v>4.2299999999999997E-2</v>
       </c>
+      <c r="V21" s="5"/>
     </row>
     <row r="22" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="B22" t="s">
-        <v>8</v>
-      </c>
       <c r="C22" s="1">
-        <v>45911</v>
+        <v>46135</v>
       </c>
       <c r="D22" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="E22" s="2">
-        <v>18.600000000000001</v>
-      </c>
-      <c r="G22">
-        <v>22.27</v>
-      </c>
-      <c r="H22" s="3">
-        <f>E23/E22-1</f>
-        <v>0.19731182795698921</v>
-      </c>
+        <v>8.49</v>
+      </c>
+      <c r="G22" s="2"/>
+      <c r="H22" s="3"/>
       <c r="I22" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="J22">
-        <v>1</v>
-      </c>
-      <c r="K22" s="5">
-        <f>H22-(R22+L22*((Q23/Q22)-1)-R22)</f>
-        <v>0.13008040603280679</v>
-      </c>
-      <c r="L22">
-        <v>0.87</v>
-      </c>
-      <c r="M22" s="3">
-        <f>H22/(DATEDIF(C22,$C$48,"d")/365)</f>
-        <v>0.32151257680491541</v>
-      </c>
-      <c r="N22" t="s">
-        <v>28</v>
-      </c>
-      <c r="O22" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="K22" s="5"/>
+      <c r="M22" s="3"/>
+      <c r="O22" s="8"/>
+      <c r="P22" s="9"/>
+      <c r="Q22" s="2">
+        <v>708.45</v>
+      </c>
+      <c r="R22" s="5"/>
+      <c r="V22" s="5"/>
+    </row>
+    <row r="23" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="B23" t="s">
+        <v>40</v>
+      </c>
+      <c r="C23" s="1">
+        <v>45897</v>
+      </c>
+      <c r="D23" t="s">
         <v>37</v>
       </c>
-      <c r="Q22" s="2">
-        <v>657.63</v>
-      </c>
-      <c r="R22" s="5">
-        <v>4.0340000000000001E-2</v>
-      </c>
-    </row>
-    <row r="23" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="C23" s="1">
-        <v>46135</v>
-      </c>
-      <c r="D23" t="s">
-        <v>31</v>
-      </c>
-      <c r="E23">
-        <v>22.27</v>
-      </c>
-      <c r="H23" s="3"/>
+      <c r="E23" s="2">
+        <v>338.84</v>
+      </c>
+      <c r="F23">
+        <v>4</v>
+      </c>
+      <c r="G23" s="2">
+        <v>172.47</v>
+      </c>
       <c r="I23" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="M23" s="3"/>
-      <c r="O23" s="8"/>
+        <v>48</v>
+      </c>
+      <c r="L23">
+        <v>3.78</v>
+      </c>
+      <c r="M23" s="3">
+        <f>H23/(DATEDIF(C23,$C$54,"d")/365)</f>
+        <v>0</v>
+      </c>
+      <c r="N23" t="s">
+        <v>41</v>
+      </c>
       <c r="Q23" s="2">
-        <v>708.45</v>
-      </c>
-      <c r="R23" s="5"/>
+        <v>647</v>
+      </c>
+      <c r="R23" s="5">
+        <v>4.2299999999999997E-2</v>
+      </c>
     </row>
     <row r="24" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B24" t="s">
-        <v>57</v>
+        <v>8</v>
       </c>
       <c r="C24" s="1">
-        <v>45922</v>
+        <v>45911</v>
       </c>
       <c r="D24" t="s">
         <v>17</v>
       </c>
       <c r="E24" s="2">
-        <v>33.72</v>
-      </c>
-      <c r="F24">
-        <v>3</v>
-      </c>
-      <c r="G24" s="2">
-        <v>38.51</v>
+        <v>18.600000000000001</v>
+      </c>
+      <c r="G24">
+        <v>22.27</v>
       </c>
       <c r="H24" s="3">
-        <f>G24/E24-1</f>
-        <v>0.14205219454329776</v>
+        <f>E25/E24-1</f>
+        <v>0.19731182795698921</v>
       </c>
       <c r="I24" s="11" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="J24">
         <v>1</v>
       </c>
       <c r="K24" s="5">
-        <f>H24-(R24+L24*((Q25/Q24)-1)-R24)</f>
-        <v>0.12109931021832041</v>
-      </c>
-      <c r="L24" s="2">
-        <v>0.3</v>
+        <f>H24-R24-L24*((Q25/Q24-1)-R24)</f>
+        <v>0.1248362060328068</v>
+      </c>
+      <c r="L24">
+        <v>0.87</v>
       </c>
       <c r="M24" s="3">
-        <f>H24/(DATEDIF(C24,$C$48,"d")/365)</f>
-        <v>0.24342277468687173</v>
+        <f>H24/(DATEDIF(C24,$C$54,"d")/365)</f>
+        <v>0.2057680491551459</v>
       </c>
       <c r="N24" t="s">
         <v>28</v>
       </c>
       <c r="O24" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q24" s="2">
-        <v>662.2</v>
+        <v>657.63</v>
       </c>
       <c r="R24" s="5">
-        <v>4.1399999999999999E-2</v>
+        <v>4.0340000000000001E-2</v>
       </c>
     </row>
     <row r="25" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C25" s="1">
-        <v>45926</v>
+        <v>46135</v>
       </c>
       <c r="D25" t="s">
-        <v>31</v>
-      </c>
-      <c r="E25" s="2">
-        <v>45.91</v>
-      </c>
-      <c r="G25" s="2"/>
+        <v>30</v>
+      </c>
+      <c r="E25">
+        <v>22.27</v>
+      </c>
       <c r="H25" s="3"/>
-      <c r="I25" s="11"/>
-      <c r="L25" s="2"/>
+      <c r="I25" s="11" t="s">
+        <v>65</v>
+      </c>
       <c r="M25" s="3"/>
       <c r="O25" s="8"/>
       <c r="Q25" s="2">
@@ -1770,67 +1778,68 @@
         <v>56</v>
       </c>
       <c r="C26" s="1">
-        <v>45926</v>
+        <v>45922</v>
       </c>
       <c r="D26" t="s">
         <v>17</v>
       </c>
       <c r="E26" s="2">
-        <v>52.8</v>
+        <v>33.72</v>
       </c>
       <c r="F26">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G26" s="2">
-        <v>17.54</v>
+        <v>45.91</v>
       </c>
       <c r="H26" s="3">
-        <f>G26/E26-1</f>
-        <v>-0.66780303030303023</v>
+        <f>E27/E26-1</f>
+        <v>0.36150652431791208</v>
       </c>
       <c r="I26" s="11" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="J26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" s="5">
-        <f>H26-(R26+L26*((Q27/Q26)-1)-R26)</f>
-        <v>-0.77653707882889433</v>
-      </c>
-      <c r="L26">
-        <v>1.45</v>
+        <f>H26-R26-L26*((Q27/Q26-1)-R26)</f>
+        <v>0.31157363999293475</v>
+      </c>
+      <c r="L26" s="2">
+        <v>0.3</v>
       </c>
       <c r="M26" s="3">
-        <f>H26/(DATEDIF(C26,$C$48,"d")/365)</f>
-        <v>-1.1662588806727563</v>
+        <f>H26/(DATEDIF(C26,$C$54,"d")/365)</f>
+        <v>0.38923268842489062</v>
       </c>
       <c r="N26" t="s">
         <v>28</v>
       </c>
-      <c r="O26" s="8"/>
+      <c r="O26" s="8" t="s">
+        <v>36</v>
+      </c>
       <c r="Q26" s="2">
-        <v>659.03</v>
+        <v>662.2</v>
       </c>
       <c r="R26" s="5">
-        <v>4.1799999999999997E-2</v>
+        <v>4.1399999999999999E-2</v>
       </c>
     </row>
     <row r="27" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C27" s="1">
-        <v>46135</v>
+        <v>45926</v>
       </c>
       <c r="D27" t="s">
-        <v>68</v>
+        <v>30</v>
       </c>
       <c r="E27" s="2">
-        <v>17.54</v>
+        <v>45.91</v>
       </c>
       <c r="G27" s="2"/>
       <c r="H27" s="3"/>
-      <c r="I27" s="11" t="s">
-        <v>69</v>
-      </c>
+      <c r="I27" s="11"/>
+      <c r="L27" s="2"/>
       <c r="M27" s="3"/>
       <c r="O27" s="8"/>
       <c r="Q27" s="2">
@@ -1840,147 +1849,141 @@
     </row>
     <row r="28" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B28" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="C28" s="1">
-        <v>46135</v>
+        <v>45926</v>
       </c>
       <c r="D28" t="s">
         <v>17</v>
       </c>
       <c r="E28" s="2">
-        <v>238.98</v>
+        <v>52.8</v>
       </c>
       <c r="F28">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G28" s="2">
-        <v>238.98</v>
-      </c>
-      <c r="H28" s="3"/>
+        <v>84.86</v>
+      </c>
+      <c r="H28" s="3">
+        <f>G28/E28-1</f>
+        <v>0.60719696969696968</v>
+      </c>
       <c r="I28" s="11" t="s">
-        <v>72</v>
+        <v>54</v>
+      </c>
+      <c r="J28">
+        <v>1</v>
+      </c>
+      <c r="K28" s="5">
+        <f>H28-R28-L28*((Q29/Q28-1)-R28)</f>
+        <v>0.51727292117110568</v>
       </c>
       <c r="L28">
-        <v>1.52</v>
-      </c>
-      <c r="M28" s="3"/>
+        <v>1.45</v>
+      </c>
+      <c r="M28" s="3">
+        <f>H28/(DATEDIF(C28,$C$54,"d")/365)</f>
+        <v>0.66157281772953414</v>
+      </c>
       <c r="N28" t="s">
-        <v>82</v>
+        <v>28</v>
       </c>
       <c r="O28" s="8"/>
       <c r="Q28" s="2">
-        <v>708.45</v>
+        <v>659.03</v>
       </c>
       <c r="R28" s="5">
-        <v>4.2999999999999997E-2</v>
+        <v>4.1799999999999997E-2</v>
       </c>
     </row>
     <row r="29" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="B29" t="s">
-        <v>71</v>
-      </c>
       <c r="C29" s="1">
         <v>46135</v>
       </c>
       <c r="D29" t="s">
-        <v>17</v>
+        <v>66</v>
       </c>
       <c r="E29" s="2">
-        <v>138.32</v>
-      </c>
-      <c r="F29">
-        <v>3</v>
-      </c>
-      <c r="G29" s="2">
-        <v>138.32</v>
-      </c>
+        <v>17.54</v>
+      </c>
+      <c r="G29" s="2"/>
       <c r="H29" s="3"/>
       <c r="I29" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="L29">
-        <v>1.05</v>
+        <v>67</v>
       </c>
       <c r="M29" s="3"/>
-      <c r="N29" t="s">
-        <v>83</v>
-      </c>
       <c r="O29" s="8"/>
       <c r="Q29" s="2">
         <v>708.45</v>
       </c>
-      <c r="R29" s="5">
-        <v>4.2999999999999997E-2</v>
-      </c>
+      <c r="R29" s="5"/>
     </row>
     <row r="30" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="B30" t="s">
-        <v>74</v>
-      </c>
       <c r="C30" s="1">
-        <v>46135</v>
+        <v>46261</v>
       </c>
       <c r="D30" t="s">
-        <v>18</v>
+        <v>66</v>
       </c>
       <c r="E30" s="2">
-        <v>78.75</v>
-      </c>
-      <c r="F30">
-        <v>5</v>
-      </c>
-      <c r="G30" s="2">
-        <v>78.75</v>
-      </c>
+        <v>84.86</v>
+      </c>
+      <c r="G30" s="2"/>
       <c r="H30" s="3"/>
       <c r="I30" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="L30">
-        <v>2.8</v>
+        <v>86</v>
       </c>
       <c r="M30" s="3"/>
-      <c r="N30" t="s">
-        <v>85</v>
-      </c>
       <c r="O30" s="8"/>
       <c r="Q30" s="2">
-        <v>708.45</v>
-      </c>
-      <c r="R30" s="5">
-        <v>4.2999999999999997E-2</v>
-      </c>
+        <v>770</v>
+      </c>
+      <c r="R30" s="5"/>
     </row>
     <row r="31" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B31" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="C31" s="1">
         <v>46135</v>
       </c>
       <c r="D31" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E31" s="2">
-        <v>403.02</v>
+        <v>238.98</v>
       </c>
       <c r="F31">
         <v>3</v>
       </c>
       <c r="G31" s="2">
-        <v>403.02</v>
-      </c>
-      <c r="H31" s="3"/>
+        <v>288.66000000000003</v>
+      </c>
+      <c r="H31" s="3">
+        <f>G31/E31-1</f>
+        <v>0.20788350489580742</v>
+      </c>
       <c r="I31" s="11" t="s">
-        <v>77</v>
+        <v>70</v>
+      </c>
+      <c r="J31">
+        <v>1</v>
+      </c>
+      <c r="K31" s="5">
+        <f>H31-R31-L31*((Q32/Q31-1)-R31)</f>
+        <v>9.8186196687747751E-2</v>
       </c>
       <c r="L31">
-        <v>3.61</v>
-      </c>
-      <c r="M31" s="3"/>
+        <v>1.52</v>
+      </c>
+      <c r="M31" s="3">
+        <f>H31/(DATEDIF(C31,$C$54,"d")/365)</f>
+        <v>0.60220221656325157</v>
+      </c>
       <c r="N31" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="O31" s="8"/>
       <c r="Q31" s="2">
@@ -1991,323 +1994,656 @@
       </c>
     </row>
     <row r="32" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="B32" t="s">
-        <v>78</v>
-      </c>
       <c r="C32" s="1">
-        <v>46135</v>
+        <v>46261</v>
       </c>
       <c r="D32" t="s">
-        <v>17</v>
+        <v>66</v>
       </c>
       <c r="E32" s="2">
-        <v>15.87</v>
-      </c>
-      <c r="F32">
-        <v>3</v>
-      </c>
-      <c r="G32" s="2">
-        <v>15.87</v>
-      </c>
+        <v>288.66000000000003</v>
+      </c>
+      <c r="G32" s="2"/>
       <c r="H32" s="3"/>
       <c r="I32" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="L32">
-        <v>1.99</v>
+        <v>87</v>
       </c>
       <c r="M32" s="3"/>
-      <c r="N32" t="s">
-        <v>28</v>
-      </c>
       <c r="O32" s="8"/>
       <c r="Q32" s="2">
-        <v>708.45</v>
-      </c>
-      <c r="R32" s="5">
-        <v>4.2999999999999997E-2</v>
-      </c>
-    </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+        <v>770</v>
+      </c>
+      <c r="R32" s="5"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B33" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="C33" s="1">
-        <v>46137</v>
+        <v>46135</v>
       </c>
       <c r="D33" t="s">
         <v>17</v>
       </c>
       <c r="E33" s="2">
-        <v>10.37</v>
+        <v>138.32</v>
       </c>
       <c r="F33">
         <v>3</v>
       </c>
       <c r="G33" s="2">
-        <v>10.37</v>
-      </c>
-      <c r="H33" s="3"/>
+        <v>225</v>
+      </c>
+      <c r="H33" s="3">
+        <f>G33/E33-1</f>
+        <v>0.62666281087333719</v>
+      </c>
       <c r="I33" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="J33">
+        <v>1</v>
+      </c>
+      <c r="K33" s="5">
+        <f>H33-R33-L33*((Q34/Q33-1)-R33)</f>
+        <v>0.53758901244013801</v>
+      </c>
+      <c r="L33">
+        <v>1.05</v>
+      </c>
+      <c r="M33" s="3">
+        <f>H33/(DATEDIF(C33,$C$54,"d")/365)</f>
+        <v>1.8153327457838735</v>
+      </c>
+      <c r="N33" t="s">
         <v>81</v>
-      </c>
-      <c r="L33">
-        <v>1.71</v>
-      </c>
-      <c r="M33" s="3"/>
-      <c r="N33" t="s">
-        <v>28</v>
       </c>
       <c r="O33" s="8"/>
       <c r="Q33" s="2">
-        <v>713.94</v>
+        <v>708.45</v>
       </c>
       <c r="R33" s="5">
         <v>4.2999999999999997E-2</v>
       </c>
     </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="C34" s="1"/>
-      <c r="E34" s="2"/>
-      <c r="I34" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="J34" s="3">
-        <f>SUM(J3:J27)/COUNT(J3:J27)</f>
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="I35" s="7"/>
-      <c r="J35" s="3"/>
-      <c r="L35" t="e" cm="1">
-        <f t="array" ref="L35">SUMPRODUCT(B2:B10, IF(A2:A10="Short",-1,1)) / COUNT(B2:B10)</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="36" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="B36" t="s">
-        <v>26</v>
-      </c>
-      <c r="F36" s="2">
-        <f>AVERAGE(F3:F21)</f>
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="H36" s="3">
-        <f>AVERAGE(H3:H26)</f>
-        <v>0.22896611277706969</v>
-      </c>
-      <c r="K36" s="5">
-        <f>AVERAGE(K3:K26)</f>
-        <v>0.12297159433774532</v>
-      </c>
-      <c r="L36" s="2">
-        <f>(SUM(L26,L24,L22,L15,L13,L9,L5,L29,L28,L32,L33)-SUM(L19,L16,L11,L7,L3,L30,L31))/18</f>
-        <v>2.4444444444444515E-2</v>
-      </c>
-      <c r="M36" s="3">
-        <f>AVERAGE(M3:M26)</f>
-        <v>2.9261830430937641</v>
-      </c>
-      <c r="V36" s="5">
-        <f>AVERAGE(V3:V15)</f>
-        <v>0.26571430959709397</v>
-      </c>
-    </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="H37" s="5"/>
-      <c r="K37" s="5"/>
-      <c r="V37" s="5"/>
-    </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="B38" t="s">
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="C34" s="1">
+        <v>46261</v>
+      </c>
+      <c r="D34" t="s">
+        <v>66</v>
+      </c>
+      <c r="E34" s="2">
+        <v>225</v>
+      </c>
+      <c r="G34" s="2"/>
+      <c r="H34" s="3"/>
+      <c r="I34" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="M34" s="3"/>
+      <c r="O34" s="8"/>
+      <c r="Q34" s="2">
+        <v>770</v>
+      </c>
+      <c r="R34" s="5"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B35" t="s">
+        <v>72</v>
+      </c>
+      <c r="C35" s="1">
+        <v>46135</v>
+      </c>
+      <c r="D35" t="s">
         <v>18</v>
       </c>
-      <c r="D38">
-        <f>COUNTIF(D3:D21,"SHORT")</f>
+      <c r="E35" s="2">
+        <v>78.75</v>
+      </c>
+      <c r="F35">
         <v>5</v>
       </c>
-      <c r="E38" s="3">
-        <f>D38/$D$40</f>
-        <v>0.55555555555555558</v>
-      </c>
-      <c r="F38" s="2">
-        <f>AVERAGE(F16:F21,F11,F7,F3)</f>
-        <v>4.166666666666667</v>
-      </c>
-      <c r="H38" s="3">
-        <f>AVERAGE(H16:H21,H11,H7,H3)</f>
-        <v>0.53928782354091642</v>
-      </c>
-      <c r="J38" s="3">
-        <f>SUM(J16:J21,J11,J7,J3)/COUNT(J16:J21,J11,J7,J3)</f>
+      <c r="G35" s="2">
+        <v>61</v>
+      </c>
+      <c r="H35" s="3">
+        <f>(E36/E35-1)*-1</f>
+        <v>0.22539682539682537</v>
+      </c>
+      <c r="I35" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="J35">
         <v>1</v>
       </c>
-      <c r="K38" s="3"/>
-      <c r="L38" s="2"/>
-      <c r="V38" s="5"/>
-    </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="K35" s="5">
+        <f>H35-R35-L35*((Q36/Q35-1)-R35)</f>
+        <v>5.9533362908294404E-2</v>
+      </c>
+      <c r="L35">
+        <v>2.8</v>
+      </c>
+      <c r="M35" s="3">
+        <f>H35/(DATEDIF(C35,$C$54,"d")/365)</f>
+        <v>0.65293524817334325</v>
+      </c>
+      <c r="N35" t="s">
+        <v>83</v>
+      </c>
+      <c r="O35" s="8"/>
+      <c r="Q35" s="2">
+        <v>708.45</v>
+      </c>
+      <c r="R35" s="5">
+        <v>4.2999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="36" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="C36" s="1">
+        <v>46261</v>
+      </c>
+      <c r="E36" s="2">
+        <v>61</v>
+      </c>
+      <c r="G36" s="2"/>
+      <c r="H36" s="3"/>
+      <c r="I36" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="M36" s="3"/>
+      <c r="O36" s="8"/>
+      <c r="Q36" s="2">
+        <v>770</v>
+      </c>
+      <c r="R36" s="5"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B37" t="s">
+        <v>74</v>
+      </c>
+      <c r="C37" s="1">
+        <v>46135</v>
+      </c>
+      <c r="D37" t="s">
+        <v>18</v>
+      </c>
+      <c r="E37" s="2">
+        <v>80</v>
+      </c>
+      <c r="F37">
+        <v>3</v>
+      </c>
+      <c r="G37" s="2">
+        <v>75</v>
+      </c>
+      <c r="H37" s="3">
+        <f>(E38/E37-1)*-1</f>
+        <v>6.25E-2</v>
+      </c>
+      <c r="I37" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="J37">
+        <v>0</v>
+      </c>
+      <c r="K37" s="5">
+        <f>H37-R37-L37*((Q38/Q37-1)-R37)</f>
+        <v>-0.13890610699414174</v>
+      </c>
+      <c r="L37">
+        <v>3.61</v>
+      </c>
+      <c r="M37" s="3">
+        <f>H37/(DATEDIF(C37,$C$54,"d")/365)</f>
+        <v>0.1810515873015873</v>
+      </c>
+      <c r="N37" t="s">
+        <v>82</v>
+      </c>
+      <c r="O37" s="8"/>
+      <c r="Q37" s="2">
+        <v>708.45</v>
+      </c>
+      <c r="R37" s="5">
+        <v>4.2999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="C38" s="1">
+        <v>46261</v>
+      </c>
+      <c r="D38" t="s">
+        <v>30</v>
+      </c>
+      <c r="E38" s="2">
+        <v>75</v>
+      </c>
+      <c r="G38" s="2"/>
+      <c r="H38" s="3"/>
+      <c r="I38" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="M38" s="3"/>
+      <c r="O38" s="8"/>
+      <c r="Q38" s="2">
+        <v>770</v>
+      </c>
+      <c r="R38" s="5"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B39" t="s">
+        <v>76</v>
+      </c>
+      <c r="C39" s="1">
+        <v>46135</v>
+      </c>
+      <c r="D39" t="s">
         <v>17</v>
       </c>
-      <c r="D39">
-        <f>COUNTIF(D3:D21,"LONG")</f>
-        <v>4</v>
-      </c>
-      <c r="E39" s="3">
-        <f>D39/$D$40</f>
-        <v>0.44444444444444442</v>
-      </c>
-      <c r="F39" s="2">
-        <f>AVERAGE(F15,F13,F9,F5)</f>
-        <v>4</v>
+      <c r="E39" s="2">
+        <v>15.87</v>
+      </c>
+      <c r="F39">
+        <v>3</v>
+      </c>
+      <c r="G39" s="2">
+        <v>13</v>
       </c>
       <c r="H39" s="3">
-        <f>AVERAGE(H15,H13,H9,H5,H22,H24,H26)</f>
-        <v>7.3077479457506834E-3</v>
-      </c>
-      <c r="J39" s="3">
-        <f>SUM(J15,J13,J9,J5,J22,J24,J26)/COUNT(J15,J13,J9,J5,J22,J24,J26)</f>
-        <v>0.5714285714285714</v>
-      </c>
-      <c r="K39" s="2"/>
-      <c r="L39" s="2"/>
-      <c r="V39" s="5"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="D40">
-        <f>SUM(D38:D39)</f>
-        <v>9</v>
-      </c>
-      <c r="H40" s="5"/>
-      <c r="K40" s="5"/>
-      <c r="V40" s="5"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+        <f>G39/E39-1</f>
+        <v>-0.1808443604284814</v>
+      </c>
+      <c r="I39" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="J39">
+        <v>0</v>
+      </c>
+      <c r="K39" s="5">
+        <f>H39-R39-L39*((Q40/Q39-1)-R39)</f>
+        <v>-0.31116517841140162</v>
+      </c>
+      <c r="L39">
+        <v>1.99</v>
+      </c>
+      <c r="M39" s="3">
+        <f>H39/(DATEDIF(C39,$C$54,"d")/365)</f>
+        <v>-0.52387453616187063</v>
+      </c>
+      <c r="N39" t="s">
+        <v>28</v>
+      </c>
+      <c r="O39" s="8"/>
+      <c r="Q39" s="2">
+        <v>708.45</v>
+      </c>
+      <c r="R39" s="5">
+        <v>4.2999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="C40" s="1">
+        <v>46261</v>
+      </c>
+      <c r="D40" t="s">
+        <v>66</v>
+      </c>
+      <c r="E40" s="2">
+        <v>13</v>
+      </c>
+      <c r="G40" s="2"/>
+      <c r="H40" s="3"/>
+      <c r="I40" s="11"/>
+      <c r="M40" s="3"/>
+      <c r="O40" s="8"/>
+      <c r="Q40" s="2">
+        <v>770</v>
+      </c>
+      <c r="R40" s="5"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B41" t="s">
-        <v>4</v>
+        <v>78</v>
       </c>
       <c r="C41" s="1">
-        <v>45862</v>
+        <v>46137</v>
+      </c>
+      <c r="D41" t="s">
+        <v>17</v>
       </c>
       <c r="E41" s="2">
-        <v>634.41999999999996</v>
+        <v>10.37</v>
+      </c>
+      <c r="F41">
+        <v>3</v>
       </c>
       <c r="G41" s="2">
-        <v>708.45</v>
+        <v>11.4</v>
       </c>
       <c r="H41" s="3">
         <f>G41/E41-1</f>
-        <v>0.11668925948110109</v>
-      </c>
-      <c r="I41" s="3"/>
+        <v>9.9324975891996292E-2</v>
+      </c>
+      <c r="I41" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="J41">
+        <v>0</v>
+      </c>
       <c r="K41" s="5">
-        <f>H41-($H$42+L41*($H$41-$H$42))</f>
+        <f>H41-R41-L41*((Q42/Q41-1)-R41)</f>
+        <v>-4.4176520599322547E-3</v>
+      </c>
+      <c r="L41">
+        <v>1.71</v>
+      </c>
+      <c r="M41" s="3">
+        <f>H41/(DATEDIF(C41,$C$54,"d")/365)</f>
+        <v>0.29236787258531166</v>
+      </c>
+      <c r="N41" t="s">
+        <v>28</v>
+      </c>
+      <c r="O41" s="8"/>
+      <c r="Q41" s="2">
+        <v>713.94</v>
+      </c>
+      <c r="R41" s="5">
+        <v>4.2999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="C42" s="1">
+        <v>46261</v>
+      </c>
+      <c r="D42" t="s">
+        <v>66</v>
+      </c>
+      <c r="E42" s="2">
+        <v>11.26</v>
+      </c>
+      <c r="G42" s="2"/>
+      <c r="H42" s="3"/>
+      <c r="I42" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="M42" s="3"/>
+      <c r="O42" s="8"/>
+      <c r="Q42" s="2">
+        <v>770</v>
+      </c>
+      <c r="R42" s="5"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B43" t="s">
+        <v>90</v>
+      </c>
+      <c r="C43" s="1">
+        <v>46261</v>
+      </c>
+      <c r="D43" t="s">
+        <v>17</v>
+      </c>
+      <c r="E43" s="2">
+        <v>114</v>
+      </c>
+      <c r="F43">
+        <v>5</v>
+      </c>
+      <c r="G43" s="2">
+        <v>110</v>
+      </c>
+      <c r="H43" s="3">
+        <f>G43/E43-1</f>
+        <v>-3.5087719298245612E-2</v>
+      </c>
+      <c r="I43" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="L43">
+        <v>1.2</v>
+      </c>
+      <c r="M43" s="3"/>
+      <c r="N43" t="s">
+        <v>29</v>
+      </c>
+      <c r="O43" s="8"/>
+      <c r="P43" s="3"/>
+      <c r="Q43" s="2">
+        <v>770</v>
+      </c>
+      <c r="R43" s="5">
+        <v>4.7E-2</v>
+      </c>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B44" t="s">
+        <v>92</v>
+      </c>
+      <c r="C44" s="1">
+        <v>46261</v>
+      </c>
+      <c r="D44" t="s">
+        <v>17</v>
+      </c>
+      <c r="E44" s="2">
+        <v>37</v>
+      </c>
+      <c r="F44">
+        <v>4</v>
+      </c>
+      <c r="G44" s="2">
+        <v>34.5</v>
+      </c>
+      <c r="H44" s="3">
+        <f>G44/E44-1</f>
+        <v>-6.7567567567567544E-2</v>
+      </c>
+      <c r="I44" s="11"/>
+      <c r="L44">
+        <v>0.33</v>
+      </c>
+      <c r="M44" s="3"/>
+      <c r="N44" t="s">
+        <v>28</v>
+      </c>
+      <c r="O44" s="8"/>
+      <c r="Q44" s="2">
+        <v>770</v>
+      </c>
+      <c r="R44" s="5">
+        <v>4.7E-2</v>
+      </c>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B45" t="s">
+        <v>93</v>
+      </c>
+      <c r="C45" s="1">
+        <v>46261</v>
+      </c>
+      <c r="D45" t="s">
+        <v>17</v>
+      </c>
+      <c r="E45" s="2">
+        <v>25</v>
+      </c>
+      <c r="F45">
+        <v>3</v>
+      </c>
+      <c r="G45" s="2">
+        <v>24</v>
+      </c>
+      <c r="H45" s="3">
+        <f>G45/E45-1</f>
+        <v>-4.0000000000000036E-2</v>
+      </c>
+      <c r="I45" s="11"/>
+      <c r="L45">
+        <v>1.53</v>
+      </c>
+      <c r="M45" s="3"/>
+      <c r="N45" t="s">
+        <v>28</v>
+      </c>
+      <c r="O45" s="8"/>
+      <c r="Q45" s="2">
+        <v>770</v>
+      </c>
+      <c r="R45" s="5">
+        <v>4.7E-2</v>
+      </c>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B46" t="s">
+        <v>94</v>
+      </c>
+      <c r="C46" s="1">
+        <v>46261</v>
+      </c>
+      <c r="D46" t="s">
+        <v>17</v>
+      </c>
+      <c r="E46" s="2">
+        <v>20</v>
+      </c>
+      <c r="F46">
+        <v>3</v>
+      </c>
+      <c r="G46" s="2">
+        <v>20</v>
+      </c>
+      <c r="H46" s="3">
+        <f>G46/E46-1</f>
         <v>0</v>
       </c>
-      <c r="L41">
+      <c r="I46" s="11"/>
+      <c r="L46">
+        <v>0.37</v>
+      </c>
+      <c r="M46" s="3"/>
+      <c r="N46" t="s">
+        <v>28</v>
+      </c>
+      <c r="O46" s="8"/>
+      <c r="Q46" s="2">
+        <v>770</v>
+      </c>
+      <c r="R46" s="5">
+        <v>4.7E-2</v>
+      </c>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="C47" s="1"/>
+      <c r="E47" s="2"/>
+      <c r="I47" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="J47" s="3">
+        <f>SUM(J3:J41)/COUNT(J3:J41)</f>
+        <v>0.72222222222222221</v>
+      </c>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="I48" s="7"/>
+      <c r="J48" s="3"/>
+      <c r="L48" t="e" cm="1">
+        <f t="array" ref="L48">SUMPRODUCT(B2:B10, IF(A2:A10="Short",-1,1)) / COUNT(B2:B10)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="49" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="B49" t="s">
+        <v>26</v>
+      </c>
+      <c r="F49" s="2">
+        <f>AVERAGE(F3:F23)</f>
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="H49" s="3">
+        <f>AVERAGE(H3:H41)</f>
+        <v>0.29635445823953649</v>
+      </c>
+      <c r="K49" s="5">
+        <f>AVERAGE(K3:K41)</f>
+        <v>0.18381583556685036</v>
+      </c>
+      <c r="L49" s="2">
+        <f>(SUM(L28,L26,L24,L16,L13,L9,L5,L33,L31,L39,L41)-SUM(L21,L18,L11,L7,L3,L35,L37))/18</f>
+        <v>2.4444444444444515E-2</v>
+      </c>
+      <c r="M49" s="3">
+        <f>AVERAGE(M3:M41)</f>
+        <v>2.2572073152971415</v>
+      </c>
+      <c r="V49" s="5">
+        <f>AVERAGE(V3:V16)</f>
+        <v>0.30994173561488547</v>
+      </c>
+    </row>
+    <row r="50" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="H50" s="5"/>
+      <c r="K50" s="5"/>
+      <c r="V50" s="5"/>
+    </row>
+    <row r="51" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="B51" t="s">
+        <v>4</v>
+      </c>
+      <c r="C51" s="1">
+        <v>45862</v>
+      </c>
+      <c r="E51" s="2">
+        <v>634.41999999999996</v>
+      </c>
+      <c r="G51" s="2">
+        <v>770</v>
+      </c>
+      <c r="H51" s="3">
+        <f>G51/E51-1</f>
+        <v>0.21370700797578901</v>
+      </c>
+      <c r="I51" s="3"/>
+      <c r="K51" s="5">
+        <f>H51-($H$52+L51*($H$51-$H$52))</f>
+        <v>0</v>
+      </c>
+      <c r="L51">
         <v>1</v>
       </c>
-      <c r="M41" s="3">
-        <f>H41/(DATEDIF(C41,$C$48,"d")/365)</f>
-        <v>0.15601311249304725</v>
-      </c>
-    </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="B42" t="s">
+      <c r="M51" s="3">
+        <f>H51/(DATEDIF(C51,$C$54,"d")/365)</f>
+        <v>0.19549638574226311</v>
+      </c>
+    </row>
+    <row r="52" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="B52" t="s">
         <v>20</v>
       </c>
-      <c r="C42" s="1"/>
-      <c r="H42" s="5">
+      <c r="C52" s="1">
+        <v>45862</v>
+      </c>
+      <c r="H52" s="5">
         <v>4.2999999999999997E-2</v>
       </c>
-      <c r="I42" s="3"/>
-      <c r="K42" s="5">
-        <f>H42-($H$42+L42*($H$41-$H$42))</f>
+      <c r="I52" s="3"/>
+      <c r="K52" s="5">
+        <f>H52-($H$52+L52*($H$51-$H$52))</f>
         <v>0</v>
       </c>
-      <c r="L42">
+      <c r="L52">
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="J43" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="B44" t="s">
-        <v>28</v>
-      </c>
-      <c r="J44" s="3">
-        <f>SUM(J3,J5,J7,J11,J13,J14)/COUNT(J3,J5,J7,J11,J13,J14)</f>
-        <v>0.8</v>
-      </c>
-      <c r="K44" s="5">
-        <f>AVERAGE(K3,K5,K7,K11,K13,K14)</f>
-        <v>0.42278500028705379</v>
-      </c>
-      <c r="L44" s="2">
-        <f>AVERAGE(L3,L5,L7,L11,L13,L14)</f>
-        <v>1.0316666666666667</v>
-      </c>
-      <c r="M44" s="3">
-        <f>AVERAGE(M3,M5,M7,M11,M13,M14)</f>
-        <v>7.0879203095733772</v>
-      </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="B45" t="s">
-        <v>29</v>
-      </c>
-      <c r="J45">
-        <f>SUM(J9)/COUNT(J9)</f>
-        <v>0</v>
-      </c>
-      <c r="K45" s="5">
-        <f>AVERAGE(K9)</f>
-        <v>-0.42721643975224455</v>
-      </c>
-      <c r="L45" s="2">
-        <f>AVERAGE(L9)</f>
-        <v>1.44</v>
-      </c>
-      <c r="M45" s="3">
-        <f>AVERAGE(M9)</f>
-        <v>-0.41412915340636403</v>
-      </c>
-    </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="B46" t="s">
-        <v>30</v>
-      </c>
-      <c r="I46" s="3"/>
-      <c r="J46">
-        <f>SUM(J15)/COUNT(J15)</f>
-        <v>1</v>
-      </c>
-      <c r="K46" s="5" t="e">
-        <f>AVERAGE(K15)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L46" s="2">
-        <f>AVERAGE(L15)</f>
-        <v>0.91</v>
-      </c>
-      <c r="M46" s="3">
-        <f>AVERAGE(M15)</f>
-        <v>0.38949576041854594</v>
-      </c>
-    </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="B48" t="s">
-        <v>62</v>
-      </c>
-      <c r="C48" s="1">
-        <v>46135</v>
-      </c>
-      <c r="K48" s="5"/>
+    <row r="54" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="B54" t="s">
+        <v>60</v>
+      </c>
+      <c r="C54" s="1">
+        <v>46261</v>
+      </c>
+      <c r="K54" s="5"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -2318,12 +2654,12 @@
     <hyperlink ref="O9" r:id="rId5" xr:uid="{C150F644-22BC-4D02-802D-BED0E57B013A}"/>
     <hyperlink ref="O11" r:id="rId6" xr:uid="{99178A6F-2964-4DD4-80DE-C47CB66DDED3}"/>
     <hyperlink ref="O13" r:id="rId7" xr:uid="{1954C073-6EE4-438F-929C-C507A342B480}"/>
-    <hyperlink ref="O15" r:id="rId8" xr:uid="{6CCCA1FE-ECD2-4689-860F-9ADE3B056949}"/>
-    <hyperlink ref="O14" r:id="rId9" xr:uid="{D35E01C5-0A43-4ACD-BD0C-88FFA33A47B9}"/>
-    <hyperlink ref="O16" r:id="rId10" xr:uid="{A047975B-CA68-4AA6-A365-A332455D0250}"/>
-    <hyperlink ref="O19" r:id="rId11" xr:uid="{E1AFF3FB-1C65-4169-8AC3-97DCAA64B9AF}"/>
-    <hyperlink ref="O22" r:id="rId12" xr:uid="{05E535AF-A000-4512-A566-52195A140416}"/>
-    <hyperlink ref="O24" r:id="rId13" xr:uid="{73FE13B3-6F8A-49A8-897D-09B2CB7F1A5F}"/>
+    <hyperlink ref="O16" r:id="rId8" xr:uid="{6CCCA1FE-ECD2-4689-860F-9ADE3B056949}"/>
+    <hyperlink ref="O15" r:id="rId9" xr:uid="{D35E01C5-0A43-4ACD-BD0C-88FFA33A47B9}"/>
+    <hyperlink ref="O18" r:id="rId10" xr:uid="{A047975B-CA68-4AA6-A365-A332455D0250}"/>
+    <hyperlink ref="O21" r:id="rId11" xr:uid="{E1AFF3FB-1C65-4169-8AC3-97DCAA64B9AF}"/>
+    <hyperlink ref="O24" r:id="rId12" xr:uid="{05E535AF-A000-4512-A566-52195A140416}"/>
+    <hyperlink ref="O26" r:id="rId13" xr:uid="{73FE13B3-6F8A-49A8-897D-09B2CB7F1A5F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId14"/>
